--- a/database/event/8037/event_8037_evp_summary.xlsx
+++ b/database/event/8037/event_8037_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>9.393700000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>4.9608</v>
       </c>
       <c r="D2" t="n">
         <v>3.3735</v>
@@ -545,7 +545,7 @@
         <v>6.1808</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>3.2641</v>
       </c>
       <c r="D3" t="n">
         <v>2.0755</v>
@@ -591,7 +591,7 @@
         <v>5.537</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2.9241</v>
       </c>
       <c r="D4" t="n">
         <v>1.8155</v>
@@ -637,7 +637,7 @@
         <v>5.5203</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>2.9152</v>
       </c>
       <c r="D5" t="n">
         <v>1.8087</v>
@@ -683,7 +683,7 @@
         <v>5.4814</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>2.8947</v>
       </c>
       <c r="D6" t="n">
         <v>1.793</v>
@@ -729,7 +729,7 @@
         <v>4.8288</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2.5501</v>
       </c>
       <c r="D7" t="n">
         <v>1.5294</v>
@@ -775,7 +775,7 @@
         <v>4.7113</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2.488</v>
       </c>
       <c r="D8" t="n">
         <v>1.4819</v>
@@ -821,7 +821,7 @@
         <v>4.4187</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2.3335</v>
       </c>
       <c r="D9" t="n">
         <v>1.3637</v>
@@ -867,7 +867,7 @@
         <v>4.3645</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2.3049</v>
       </c>
       <c r="D10" t="n">
         <v>1.3418</v>
@@ -913,7 +913,7 @@
         <v>4.3432</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2.2936</v>
       </c>
       <c r="D11" t="n">
         <v>1.3332</v>
@@ -959,7 +959,7 @@
         <v>4.125</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>2.1784</v>
       </c>
       <c r="D12" t="n">
         <v>1.245</v>
@@ -1005,7 +1005,7 @@
         <v>4.1022</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2.1664</v>
       </c>
       <c r="D13" t="n">
         <v>1.2358</v>
@@ -1051,7 +1051,7 @@
         <v>3.9558</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>2.089</v>
       </c>
       <c r="D14" t="n">
         <v>1.1767</v>
@@ -1097,7 +1097,7 @@
         <v>3.9261</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>2.0734</v>
       </c>
       <c r="D15" t="n">
         <v>1.1647</v>
@@ -1143,7 +1143,7 @@
         <v>3.8851</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.0517</v>
       </c>
       <c r="D16" t="n">
         <v>1.1481</v>
@@ -1189,7 +1189,7 @@
         <v>3.4888</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1.8424</v>
       </c>
       <c r="D17" t="n">
         <v>0.988</v>
@@ -1235,7 +1235,7 @@
         <v>3.2794</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1.7318</v>
       </c>
       <c r="D18" t="n">
         <v>0.9034</v>
@@ -1281,7 +1281,7 @@
         <v>2.777</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1.4665</v>
       </c>
       <c r="D19" t="n">
         <v>0.7005</v>
@@ -1327,7 +1327,7 @@
         <v>2.6492</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1.399</v>
       </c>
       <c r="D20" t="n">
         <v>0.6489</v>
@@ -1373,7 +1373,7 @@
         <v>2.6305</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.3892</v>
       </c>
       <c r="D21" t="n">
         <v>0.6413</v>
@@ -1419,7 +1419,7 @@
         <v>2.5995</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1.3728</v>
       </c>
       <c r="D22" t="n">
         <v>0.6288</v>
@@ -1465,7 +1465,7 @@
         <v>2.5575</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1.3506</v>
       </c>
       <c r="D23" t="n">
         <v>0.6118</v>
@@ -1511,7 +1511,7 @@
         <v>2.3519</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1.242</v>
       </c>
       <c r="D24" t="n">
         <v>0.5288</v>
@@ -1557,7 +1557,7 @@
         <v>2.2578</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1.1923</v>
       </c>
       <c r="D25" t="n">
         <v>0.4907</v>
@@ -1603,7 +1603,7 @@
         <v>2.1661</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1.1439</v>
       </c>
       <c r="D26" t="n">
         <v>0.4537</v>
@@ -1649,7 +1649,7 @@
         <v>2.157</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1.1391</v>
       </c>
       <c r="D27" t="n">
         <v>0.45</v>
@@ -1695,7 +1695,7 @@
         <v>1.9993</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1.0558</v>
       </c>
       <c r="D28" t="n">
         <v>0.3863</v>
@@ -1741,7 +1741,7 @@
         <v>1.8848</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.9954</v>
       </c>
       <c r="D29" t="n">
         <v>0.3401</v>
@@ -1787,7 +1787,7 @@
         <v>1.6669</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.8803</v>
       </c>
       <c r="D30" t="n">
         <v>0.252</v>
@@ -1833,7 +1833,7 @@
         <v>1.5298</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.8079</v>
       </c>
       <c r="D31" t="n">
         <v>0.1966</v>
@@ -1879,7 +1879,7 @@
         <v>1.4878</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.7857</v>
       </c>
       <c r="D32" t="n">
         <v>0.1797</v>
@@ -1925,7 +1925,7 @@
         <v>1.4858</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.7846</v>
       </c>
       <c r="D33" t="n">
         <v>0.1789</v>
@@ -1971,7 +1971,7 @@
         <v>1.3418</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.7086</v>
       </c>
       <c r="D34" t="n">
         <v>0.1207</v>
@@ -2017,7 +2017,7 @@
         <v>1.2585</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.6646</v>
       </c>
       <c r="D35" t="n">
         <v>0.08699999999999999</v>
@@ -2063,7 +2063,7 @@
         <v>1.2344</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.6519</v>
       </c>
       <c r="D36" t="n">
         <v>0.07729999999999999</v>
@@ -2109,7 +2109,7 @@
         <v>1.1871</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.6269</v>
       </c>
       <c r="D37" t="n">
         <v>0.0582</v>
@@ -2155,7 +2155,7 @@
         <v>1.0438</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.5512</v>
       </c>
       <c r="D38" t="n">
         <v>0.0003</v>
@@ -2201,7 +2201,7 @@
         <v>1.0298</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.5438</v>
       </c>
       <c r="D39" t="n">
         <v>-0.0053</v>
@@ -2247,7 +2247,7 @@
         <v>1.0194</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.5383</v>
       </c>
       <c r="D40" t="n">
         <v>-0.0095</v>
@@ -2293,7 +2293,7 @@
         <v>0.8487</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.4482</v>
       </c>
       <c r="D41" t="n">
         <v>-0.0785</v>
@@ -2339,7 +2339,7 @@
         <v>0.7176</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.379</v>
       </c>
       <c r="D42" t="n">
         <v>-0.1315</v>
@@ -2385,7 +2385,7 @@
         <v>0.6665</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.352</v>
       </c>
       <c r="D43" t="n">
         <v>-0.1521</v>
@@ -2431,7 +2431,7 @@
         <v>0.5597</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.2956</v>
       </c>
       <c r="D44" t="n">
         <v>-0.1953</v>
@@ -2477,7 +2477,7 @@
         <v>0.5231</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.2762</v>
       </c>
       <c r="D45" t="n">
         <v>-0.21</v>
@@ -2523,7 +2523,7 @@
         <v>0.358</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.1891</v>
       </c>
       <c r="D46" t="n">
         <v>-0.2767</v>
@@ -2569,7 +2569,7 @@
         <v>0.2912</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.1538</v>
       </c>
       <c r="D47" t="n">
         <v>-0.3037</v>
@@ -2615,7 +2615,7 @@
         <v>0.2849</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.1505</v>
       </c>
       <c r="D48" t="n">
         <v>-0.3063</v>
@@ -2661,7 +2661,7 @@
         <v>0.2299</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.1214</v>
       </c>
       <c r="D49" t="n">
         <v>-0.3285</v>
@@ -2707,7 +2707,7 @@
         <v>-0.0368</v>
       </c>
       <c r="C50" t="n">
-        <v>-0</v>
+        <v>-0.0194</v>
       </c>
       <c r="D50" t="n">
         <v>-0.4362</v>
@@ -2753,7 +2753,7 @@
         <v>-0.1493</v>
       </c>
       <c r="C51" t="n">
-        <v>-0</v>
+        <v>-0.0788</v>
       </c>
       <c r="D51" t="n">
         <v>-0.4817</v>
@@ -2799,7 +2799,7 @@
         <v>-0.3684</v>
       </c>
       <c r="C52" t="n">
-        <v>-0</v>
+        <v>-0.1946</v>
       </c>
       <c r="D52" t="n">
         <v>-0.5702</v>
@@ -2845,7 +2845,7 @@
         <v>-0.3804</v>
       </c>
       <c r="C53" t="n">
-        <v>-0</v>
+        <v>-0.2009</v>
       </c>
       <c r="D53" t="n">
         <v>-0.575</v>
@@ -2891,7 +2891,7 @@
         <v>-0.4381</v>
       </c>
       <c r="C54" t="n">
-        <v>-0</v>
+        <v>-0.2314</v>
       </c>
       <c r="D54" t="n">
         <v>-0.5983000000000001</v>
@@ -2937,7 +2937,7 @@
         <v>-0.4487</v>
       </c>
       <c r="C55" t="n">
-        <v>-0</v>
+        <v>-0.237</v>
       </c>
       <c r="D55" t="n">
         <v>-0.6026</v>
@@ -2983,7 +2983,7 @@
         <v>-0.4566</v>
       </c>
       <c r="C56" t="n">
-        <v>-0</v>
+        <v>-0.2411</v>
       </c>
       <c r="D56" t="n">
         <v>-0.6058</v>
@@ -3029,7 +3029,7 @@
         <v>-0.471</v>
       </c>
       <c r="C57" t="n">
-        <v>-0</v>
+        <v>-0.2487</v>
       </c>
       <c r="D57" t="n">
         <v>-0.6116</v>
@@ -3075,7 +3075,7 @@
         <v>-0.5347</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.2824</v>
       </c>
       <c r="D58" t="n">
         <v>-0.6374</v>
@@ -3121,7 +3121,7 @@
         <v>-0.5508</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.2909</v>
       </c>
       <c r="D59" t="n">
         <v>-0.6439</v>
@@ -3167,7 +3167,7 @@
         <v>-0.5593</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.2954</v>
       </c>
       <c r="D60" t="n">
         <v>-0.6473</v>
@@ -3213,7 +3213,7 @@
         <v>-0.5643</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.298</v>
       </c>
       <c r="D61" t="n">
         <v>-0.6493</v>
@@ -3259,7 +3259,7 @@
         <v>-0.6343</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.335</v>
       </c>
       <c r="D62" t="n">
         <v>-0.6776</v>
@@ -3305,7 +3305,7 @@
         <v>-0.8133</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.4295</v>
       </c>
       <c r="D63" t="n">
         <v>-0.7499</v>
@@ -3351,7 +3351,7 @@
         <v>-0.8198</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.4329</v>
       </c>
       <c r="D64" t="n">
         <v>-0.7524999999999999</v>
@@ -3397,7 +3397,7 @@
         <v>-0.9073</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.4791</v>
       </c>
       <c r="D65" t="n">
         <v>-0.7879</v>
@@ -3443,7 +3443,7 @@
         <v>-0.9658</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.51</v>
       </c>
       <c r="D66" t="n">
         <v>-0.8115</v>
@@ -3489,7 +3489,7 @@
         <v>-1.2038</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.6357</v>
       </c>
       <c r="D67" t="n">
         <v>-0.9077</v>
@@ -3535,7 +3535,7 @@
         <v>-1.2069</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.6374</v>
       </c>
       <c r="D68" t="n">
         <v>-0.9089</v>
@@ -3581,7 +3581,7 @@
         <v>-1.2262</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.6476</v>
       </c>
       <c r="D69" t="n">
         <v>-0.9167</v>
@@ -3627,7 +3627,7 @@
         <v>-1.2372</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.6534</v>
       </c>
       <c r="D70" t="n">
         <v>-0.9212</v>
@@ -3673,7 +3673,7 @@
         <v>-1.2381</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-0.6538</v>
       </c>
       <c r="D71" t="n">
         <v>-0.9215</v>
@@ -3719,7 +3719,7 @@
         <v>-1.3184</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-0.6962</v>
       </c>
       <c r="D72" t="n">
         <v>-0.954</v>
@@ -3765,7 +3765,7 @@
         <v>-1.5043</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-0.7944</v>
       </c>
       <c r="D73" t="n">
         <v>-1.0291</v>
@@ -3811,7 +3811,7 @@
         <v>-1.5527</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-0.82</v>
       </c>
       <c r="D74" t="n">
         <v>-1.0486</v>
@@ -3857,7 +3857,7 @@
         <v>-1.6535</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-0.8732</v>
       </c>
       <c r="D75" t="n">
         <v>-1.0893</v>
@@ -3903,7 +3903,7 @@
         <v>-1.6795</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-0.8869</v>
       </c>
       <c r="D76" t="n">
         <v>-1.0998</v>
@@ -3949,7 +3949,7 @@
         <v>-1.7593</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-0.9291</v>
       </c>
       <c r="D77" t="n">
         <v>-1.1321</v>
@@ -3995,7 +3995,7 @@
         <v>-2.1718</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-1.1469</v>
       </c>
       <c r="D78" t="n">
         <v>-1.2987</v>
@@ -4041,7 +4041,7 @@
         <v>-2.7334</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-1.4435</v>
       </c>
       <c r="D79" t="n">
         <v>-1.5256</v>
@@ -4087,7 +4087,7 @@
         <v>-3.1049</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-1.6397</v>
       </c>
       <c r="D80" t="n">
         <v>-1.6757</v>
@@ -4133,7 +4133,7 @@
         <v>-3.9995</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-2.1121</v>
       </c>
       <c r="D81" t="n">
         <v>-2.0371</v>

--- a/database/event/8037/event_8037_evp_summary.xlsx
+++ b/database/event/8037/event_8037_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>4.9608</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3735</v>
+        <v>3.2985</v>
       </c>
       <c r="E2" t="n">
         <v>9.393700000000001</v>
@@ -548,7 +548,7 @@
         <v>3.2641</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0755</v>
+        <v>2.0185</v>
       </c>
       <c r="E3" t="n">
         <v>6.1808</v>
@@ -584,93 +584,93 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.537</v>
+        <v>5.5203</v>
       </c>
       <c r="C4" t="n">
-        <v>2.9241</v>
+        <v>2.9152</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8155</v>
+        <v>1.7554</v>
       </c>
       <c r="E4" t="n">
-        <v>5.537</v>
+        <v>5.5203</v>
       </c>
       <c r="F4" t="n">
-        <v>5.2333</v>
+        <v>4.3238</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3037</v>
+        <v>1.1965</v>
       </c>
       <c r="H4" t="n">
-        <v>5.9027</v>
+        <v>4.835</v>
       </c>
       <c r="I4" t="n">
-        <v>5.9855</v>
+        <v>3.9189</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3037</v>
+        <v>1.1965</v>
       </c>
       <c r="K4" t="n">
-        <v>199</v>
+        <v>154</v>
       </c>
       <c r="L4" t="n">
-        <v>43</v>
+        <v>130</v>
       </c>
       <c r="M4" t="n">
-        <v>6.2892</v>
+        <v>5.115399999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>242</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.5203</v>
+        <v>5.495</v>
       </c>
       <c r="C5" t="n">
-        <v>2.9152</v>
+        <v>2.9019</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8087</v>
+        <v>1.7453</v>
       </c>
       <c r="E5" t="n">
-        <v>5.5203</v>
+        <v>5.495</v>
       </c>
       <c r="F5" t="n">
-        <v>4.3238</v>
+        <v>5.1913</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1965</v>
+        <v>0.3037</v>
       </c>
       <c r="H5" t="n">
-        <v>4.835</v>
+        <v>5.8369</v>
       </c>
       <c r="I5" t="n">
-        <v>3.9189</v>
+        <v>5.9855</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1965</v>
+        <v>0.3037</v>
       </c>
       <c r="K5" t="n">
-        <v>154</v>
+        <v>199</v>
       </c>
       <c r="L5" t="n">
-        <v>130</v>
+        <v>43</v>
       </c>
       <c r="M5" t="n">
-        <v>5.115399999999999</v>
+        <v>6.2892</v>
       </c>
       <c r="N5" t="n">
-        <v>284</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6">
@@ -686,7 +686,7 @@
         <v>2.8947</v>
       </c>
       <c r="D6" t="n">
-        <v>1.793</v>
+        <v>1.7399</v>
       </c>
       <c r="E6" t="n">
         <v>5.4814</v>
@@ -732,7 +732,7 @@
         <v>2.5501</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5294</v>
+        <v>1.4799</v>
       </c>
       <c r="E7" t="n">
         <v>4.8288</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.7113</v>
+        <v>4.6979</v>
       </c>
       <c r="C8" t="n">
-        <v>2.488</v>
+        <v>2.4809</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4819</v>
+        <v>1.4277</v>
       </c>
       <c r="E8" t="n">
-        <v>4.7113</v>
+        <v>4.6979</v>
       </c>
       <c r="F8" t="n">
-        <v>3.5775</v>
+        <v>3.5641</v>
       </c>
       <c r="G8" t="n">
         <v>1.1338</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5775</v>
+        <v>3.5641</v>
       </c>
       <c r="I8" t="n">
         <v>3.5941</v>
@@ -824,7 +824,7 @@
         <v>2.3335</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3637</v>
+        <v>1.3165</v>
       </c>
       <c r="E9" t="n">
         <v>4.4187</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.3645</v>
+        <v>4.343</v>
       </c>
       <c r="C10" t="n">
-        <v>2.3049</v>
+        <v>2.2935</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3418</v>
+        <v>1.2863</v>
       </c>
       <c r="E10" t="n">
-        <v>4.3645</v>
+        <v>4.343</v>
       </c>
       <c r="F10" t="n">
-        <v>4.3645</v>
+        <v>4.343</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>4.5405</v>
+        <v>4.5067</v>
       </c>
       <c r="I10" t="n">
         <v>4.5829</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.3432</v>
+        <v>4.303</v>
       </c>
       <c r="C11" t="n">
-        <v>2.2936</v>
+        <v>2.2724</v>
       </c>
       <c r="D11" t="n">
-        <v>1.3332</v>
+        <v>1.2704</v>
       </c>
       <c r="E11" t="n">
-        <v>4.3432</v>
+        <v>4.303</v>
       </c>
       <c r="F11" t="n">
-        <v>3.6</v>
+        <v>3.5598</v>
       </c>
       <c r="G11" t="n">
         <v>0.7432</v>
       </c>
       <c r="H11" t="n">
-        <v>3.6</v>
+        <v>3.5598</v>
       </c>
       <c r="I11" t="n">
         <v>3.6505</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.125</v>
+        <v>4.1151</v>
       </c>
       <c r="C12" t="n">
-        <v>2.1784</v>
+        <v>2.1732</v>
       </c>
       <c r="D12" t="n">
-        <v>1.245</v>
+        <v>1.1955</v>
       </c>
       <c r="E12" t="n">
-        <v>4.125</v>
+        <v>4.1151</v>
       </c>
       <c r="F12" t="n">
-        <v>4.125</v>
+        <v>4.1151</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>4.1649</v>
+        <v>4.1494</v>
       </c>
       <c r="I12" t="n">
         <v>4.1843</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.1022</v>
+        <v>4.0954</v>
       </c>
       <c r="C13" t="n">
-        <v>2.1664</v>
+        <v>2.1628</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2358</v>
+        <v>1.1877</v>
       </c>
       <c r="E13" t="n">
-        <v>4.1022</v>
+        <v>4.0954</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8272</v>
+        <v>1.8204</v>
       </c>
       <c r="G13" t="n">
         <v>2.275</v>
       </c>
       <c r="H13" t="n">
-        <v>1.8272</v>
+        <v>1.8204</v>
       </c>
       <c r="I13" t="n">
         <v>1.8357</v>
@@ -1054,7 +1054,7 @@
         <v>2.089</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1767</v>
+        <v>1.1321</v>
       </c>
       <c r="E14" t="n">
         <v>3.9558</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.9261</v>
+        <v>3.8969</v>
       </c>
       <c r="C15" t="n">
-        <v>2.0734</v>
+        <v>2.0579</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1647</v>
+        <v>1.1086</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9261</v>
+        <v>3.8969</v>
       </c>
       <c r="F15" t="n">
-        <v>3.9261</v>
+        <v>3.8969</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.9261</v>
+        <v>3.8969</v>
       </c>
       <c r="I15" t="n">
         <v>3.9627</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.8851</v>
+        <v>3.8554</v>
       </c>
       <c r="C16" t="n">
-        <v>2.0517</v>
+        <v>2.036</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1481</v>
+        <v>1.0921</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8851</v>
+        <v>3.8554</v>
       </c>
       <c r="F16" t="n">
-        <v>4.1303</v>
+        <v>4.1006</v>
       </c>
       <c r="G16" t="n">
         <v>-0.2452</v>
       </c>
       <c r="H16" t="n">
-        <v>4.1732</v>
+        <v>4.1267</v>
       </c>
       <c r="I16" t="n">
         <v>4.2318</v>
@@ -1192,7 +1192,7 @@
         <v>1.8424</v>
       </c>
       <c r="D17" t="n">
-        <v>0.988</v>
+        <v>0.946</v>
       </c>
       <c r="E17" t="n">
         <v>3.4888</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.2794</v>
+        <v>3.2578</v>
       </c>
       <c r="C18" t="n">
-        <v>1.7318</v>
+        <v>1.7204</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9034</v>
+        <v>0.854</v>
       </c>
       <c r="E18" t="n">
-        <v>3.2794</v>
+        <v>3.2578</v>
       </c>
       <c r="F18" t="n">
-        <v>2.899</v>
+        <v>2.8774</v>
       </c>
       <c r="G18" t="n">
         <v>0.3804</v>
       </c>
       <c r="H18" t="n">
-        <v>2.899</v>
+        <v>2.8774</v>
       </c>
       <c r="I18" t="n">
         <v>2.926</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.777</v>
+        <v>2.769</v>
       </c>
       <c r="C19" t="n">
-        <v>1.4665</v>
+        <v>1.4623</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7005</v>
+        <v>0.6593</v>
       </c>
       <c r="E19" t="n">
-        <v>2.777</v>
+        <v>2.769</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1596</v>
+        <v>2.1516</v>
       </c>
       <c r="G19" t="n">
         <v>0.6173999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1596</v>
+        <v>2.1516</v>
       </c>
       <c r="I19" t="n">
         <v>2.1697</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.6492</v>
+        <v>2.6294</v>
       </c>
       <c r="C20" t="n">
-        <v>1.399</v>
+        <v>1.3886</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6489</v>
+        <v>0.6036</v>
       </c>
       <c r="E20" t="n">
-        <v>2.6492</v>
+        <v>2.6294</v>
       </c>
       <c r="F20" t="n">
-        <v>2.6492</v>
+        <v>2.6294</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.6492</v>
+        <v>2.6294</v>
       </c>
       <c r="I20" t="n">
         <v>2.6739</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.6305</v>
+        <v>2.6051</v>
       </c>
       <c r="C21" t="n">
-        <v>1.3892</v>
+        <v>1.3757</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6413</v>
+        <v>0.594</v>
       </c>
       <c r="E21" t="n">
-        <v>2.6305</v>
+        <v>2.6051</v>
       </c>
       <c r="F21" t="n">
-        <v>3.4026</v>
+        <v>3.3772</v>
       </c>
       <c r="G21" t="n">
         <v>-0.7721</v>
       </c>
       <c r="H21" t="n">
-        <v>3.4026</v>
+        <v>3.3772</v>
       </c>
       <c r="I21" t="n">
         <v>3.4343</v>
@@ -1422,7 +1422,7 @@
         <v>1.3728</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6288</v>
+        <v>0.5917</v>
       </c>
       <c r="E22" t="n">
         <v>2.5995</v>
@@ -1468,7 +1468,7 @@
         <v>1.3506</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6118</v>
+        <v>0.575</v>
       </c>
       <c r="E23" t="n">
         <v>2.5575</v>
@@ -1514,7 +1514,7 @@
         <v>1.242</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5288</v>
+        <v>0.4931</v>
       </c>
       <c r="E24" t="n">
         <v>2.3519</v>
@@ -1560,7 +1560,7 @@
         <v>1.1923</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4907</v>
+        <v>0.4556</v>
       </c>
       <c r="E25" t="n">
         <v>2.2578</v>
@@ -1596,93 +1596,93 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.1661</v>
+        <v>2.157</v>
       </c>
       <c r="C26" t="n">
-        <v>1.1439</v>
+        <v>1.1391</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4537</v>
+        <v>0.4154</v>
       </c>
       <c r="E26" t="n">
-        <v>2.1661</v>
+        <v>2.157</v>
       </c>
       <c r="F26" t="n">
-        <v>1.2587</v>
+        <v>2.157</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9074</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.2587</v>
+        <v>2.157</v>
       </c>
       <c r="I26" t="n">
-        <v>1.2705</v>
+        <v>2.157</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9074</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>240</v>
+        <v>158</v>
       </c>
       <c r="L26" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.1779</v>
+        <v>2.157</v>
       </c>
       <c r="N26" t="n">
-        <v>304</v>
+        <v>158</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.157</v>
+        <v>2.1567</v>
       </c>
       <c r="C27" t="n">
-        <v>1.1391</v>
+        <v>1.1389</v>
       </c>
       <c r="D27" t="n">
-        <v>0.45</v>
+        <v>0.4153</v>
       </c>
       <c r="E27" t="n">
-        <v>2.157</v>
+        <v>2.1567</v>
       </c>
       <c r="F27" t="n">
-        <v>2.157</v>
+        <v>1.2493</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.9074</v>
       </c>
       <c r="H27" t="n">
-        <v>2.157</v>
+        <v>1.2493</v>
       </c>
       <c r="I27" t="n">
-        <v>2.157</v>
+        <v>1.2705</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.9074</v>
       </c>
       <c r="K27" t="n">
-        <v>158</v>
+        <v>240</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M27" t="n">
-        <v>2.157</v>
+        <v>2.1779</v>
       </c>
       <c r="N27" t="n">
-        <v>158</v>
+        <v>304</v>
       </c>
     </row>
     <row r="28">
@@ -1698,7 +1698,7 @@
         <v>1.0558</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3863</v>
+        <v>0.3526</v>
       </c>
       <c r="E28" t="n">
         <v>1.9993</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.8848</v>
+        <v>1.8805</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9954</v>
+        <v>0.9931</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3401</v>
+        <v>0.3053</v>
       </c>
       <c r="E29" t="n">
-        <v>1.8848</v>
+        <v>1.8805</v>
       </c>
       <c r="F29" t="n">
-        <v>1.1408</v>
+        <v>1.1365</v>
       </c>
       <c r="G29" t="n">
         <v>0.744</v>
       </c>
       <c r="H29" t="n">
-        <v>1.1408</v>
+        <v>1.1365</v>
       </c>
       <c r="I29" t="n">
         <v>1.1461</v>
@@ -1790,7 +1790,7 @@
         <v>0.8803</v>
       </c>
       <c r="D30" t="n">
-        <v>0.252</v>
+        <v>0.2202</v>
       </c>
       <c r="E30" t="n">
         <v>1.6669</v>
@@ -1836,7 +1836,7 @@
         <v>0.8079</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1966</v>
+        <v>0.1656</v>
       </c>
       <c r="E31" t="n">
         <v>1.5298</v>
@@ -1882,7 +1882,7 @@
         <v>0.7857</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1797</v>
+        <v>0.1488</v>
       </c>
       <c r="E32" t="n">
         <v>1.4878</v>
@@ -1928,7 +1928,7 @@
         <v>0.7846</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1789</v>
+        <v>0.148</v>
       </c>
       <c r="E33" t="n">
         <v>1.4858</v>
@@ -1974,7 +1974,7 @@
         <v>0.7086</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1207</v>
+        <v>0.0907</v>
       </c>
       <c r="E34" t="n">
         <v>1.3418</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.2585</v>
+        <v>1.2538</v>
       </c>
       <c r="C35" t="n">
-        <v>0.6646</v>
+        <v>0.6621</v>
       </c>
       <c r="D35" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0556</v>
       </c>
       <c r="E35" t="n">
-        <v>1.2585</v>
+        <v>1.2538</v>
       </c>
       <c r="F35" t="n">
-        <v>1.2585</v>
+        <v>1.2538</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.2585</v>
+        <v>1.2538</v>
       </c>
       <c r="I35" t="n">
         <v>1.2644</v>
@@ -2066,7 +2066,7 @@
         <v>0.6519</v>
       </c>
       <c r="D36" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0479</v>
       </c>
       <c r="E36" t="n">
         <v>1.2344</v>
@@ -2112,7 +2112,7 @@
         <v>0.6269</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0582</v>
+        <v>0.029</v>
       </c>
       <c r="E37" t="n">
         <v>1.1871</v>
@@ -2158,7 +2158,7 @@
         <v>0.5512</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0003</v>
+        <v>-0.0281</v>
       </c>
       <c r="E38" t="n">
         <v>1.0438</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.0298</v>
+        <v>1.0259</v>
       </c>
       <c r="C39" t="n">
-        <v>0.5438</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0053</v>
+        <v>-0.0352</v>
       </c>
       <c r="E39" t="n">
-        <v>1.0298</v>
+        <v>1.0259</v>
       </c>
       <c r="F39" t="n">
-        <v>1.0298</v>
+        <v>1.0259</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.0298</v>
+        <v>1.0259</v>
       </c>
       <c r="I39" t="n">
         <v>1.0346</v>
@@ -2250,7 +2250,7 @@
         <v>0.5383</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.0095</v>
+        <v>-0.0378</v>
       </c>
       <c r="E40" t="n">
         <v>1.0194</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8487</v>
+        <v>0.8429</v>
       </c>
       <c r="C41" t="n">
-        <v>0.4482</v>
+        <v>0.4451</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.0785</v>
+        <v>-0.1081</v>
       </c>
       <c r="E41" t="n">
-        <v>0.8487</v>
+        <v>0.8429</v>
       </c>
       <c r="F41" t="n">
-        <v>1.5642</v>
+        <v>1.5584</v>
       </c>
       <c r="G41" t="n">
         <v>-0.7155</v>
       </c>
       <c r="H41" t="n">
-        <v>1.5642</v>
+        <v>1.5584</v>
       </c>
       <c r="I41" t="n">
         <v>1.5715</v>
@@ -2336,25 +2336,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7176</v>
+        <v>0.7149</v>
       </c>
       <c r="C42" t="n">
-        <v>0.379</v>
+        <v>0.3775</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1315</v>
+        <v>-0.1591</v>
       </c>
       <c r="E42" t="n">
-        <v>0.7176</v>
+        <v>0.7149</v>
       </c>
       <c r="F42" t="n">
-        <v>0.7176</v>
+        <v>0.7149</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.7176</v>
+        <v>0.7149</v>
       </c>
       <c r="I42" t="n">
         <v>0.7209</v>
@@ -2388,7 +2388,7 @@
         <v>0.352</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1521</v>
+        <v>-0.1784</v>
       </c>
       <c r="E43" t="n">
         <v>0.6665</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5597</v>
+        <v>0.5555</v>
       </c>
       <c r="C44" t="n">
-        <v>0.2956</v>
+        <v>0.2934</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1953</v>
+        <v>-0.2226</v>
       </c>
       <c r="E44" t="n">
-        <v>0.5597</v>
+        <v>0.5555</v>
       </c>
       <c r="F44" t="n">
-        <v>0.5597</v>
+        <v>0.5555</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.5597</v>
+        <v>0.5555</v>
       </c>
       <c r="I44" t="n">
         <v>0.5649</v>
@@ -2480,7 +2480,7 @@
         <v>0.2762</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.21</v>
+        <v>-0.2355</v>
       </c>
       <c r="E45" t="n">
         <v>0.5231</v>
@@ -2526,7 +2526,7 @@
         <v>0.1891</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2767</v>
+        <v>-0.3013</v>
       </c>
       <c r="E46" t="n">
         <v>0.358</v>
@@ -2572,7 +2572,7 @@
         <v>0.1538</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3037</v>
+        <v>-0.3279</v>
       </c>
       <c r="E47" t="n">
         <v>0.2912</v>
@@ -2618,7 +2618,7 @@
         <v>0.1505</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3063</v>
+        <v>-0.3304</v>
       </c>
       <c r="E48" t="n">
         <v>0.2849</v>
@@ -2664,7 +2664,7 @@
         <v>0.1214</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3285</v>
+        <v>-0.3523</v>
       </c>
       <c r="E49" t="n">
         <v>0.2299</v>
@@ -2710,7 +2710,7 @@
         <v>-0.0194</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4362</v>
+        <v>-0.4586</v>
       </c>
       <c r="E50" t="n">
         <v>-0.0368</v>
@@ -2756,7 +2756,7 @@
         <v>-0.0788</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4817</v>
+        <v>-0.5034</v>
       </c>
       <c r="E51" t="n">
         <v>-0.1493</v>
@@ -2802,7 +2802,7 @@
         <v>-0.1946</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5702</v>
+        <v>-0.5907</v>
       </c>
       <c r="E52" t="n">
         <v>-0.3684</v>
@@ -2848,7 +2848,7 @@
         <v>-0.2009</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.575</v>
+        <v>-0.5955</v>
       </c>
       <c r="E53" t="n">
         <v>-0.3804</v>
@@ -2894,7 +2894,7 @@
         <v>-0.2314</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="E54" t="n">
         <v>-0.4381</v>
@@ -2940,7 +2940,7 @@
         <v>-0.237</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.6026</v>
+        <v>-0.6227</v>
       </c>
       <c r="E55" t="n">
         <v>-0.4487</v>
@@ -2986,7 +2986,7 @@
         <v>-0.2411</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6058</v>
+        <v>-0.6258</v>
       </c>
       <c r="E56" t="n">
         <v>-0.4566</v>
@@ -3032,7 +3032,7 @@
         <v>-0.2487</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6116</v>
+        <v>-0.6316000000000001</v>
       </c>
       <c r="E57" t="n">
         <v>-0.471</v>
@@ -3078,7 +3078,7 @@
         <v>-0.2824</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6374</v>
+        <v>-0.6569</v>
       </c>
       <c r="E58" t="n">
         <v>-0.5347</v>
@@ -3124,7 +3124,7 @@
         <v>-0.2909</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6439</v>
+        <v>-0.6633</v>
       </c>
       <c r="E59" t="n">
         <v>-0.5508</v>
@@ -3170,7 +3170,7 @@
         <v>-0.2954</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6473</v>
+        <v>-0.6667</v>
       </c>
       <c r="E60" t="n">
         <v>-0.5593</v>
@@ -3216,7 +3216,7 @@
         <v>-0.298</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6493</v>
+        <v>-0.6687</v>
       </c>
       <c r="E61" t="n">
         <v>-0.5643</v>
@@ -3256,25 +3256,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.6343</v>
+        <v>-0.632</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.335</v>
+        <v>-0.3338</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6776</v>
+        <v>-0.6957</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.6343</v>
+        <v>-0.632</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.6343</v>
+        <v>-0.632</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.6343</v>
+        <v>-0.632</v>
       </c>
       <c r="I62" t="n">
         <v>-0.6373</v>
@@ -3308,7 +3308,7 @@
         <v>-0.4295</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7499</v>
+        <v>-0.7679</v>
       </c>
       <c r="E63" t="n">
         <v>-0.8133</v>
@@ -3354,7 +3354,7 @@
         <v>-0.4329</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7524999999999999</v>
+        <v>-0.7705</v>
       </c>
       <c r="E64" t="n">
         <v>-0.8198</v>
@@ -3400,7 +3400,7 @@
         <v>-0.4791</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7879</v>
+        <v>-0.8054</v>
       </c>
       <c r="E65" t="n">
         <v>-0.9073</v>
@@ -3446,7 +3446,7 @@
         <v>-0.51</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8115</v>
+        <v>-0.8287</v>
       </c>
       <c r="E66" t="n">
         <v>-0.9658</v>
@@ -3492,7 +3492,7 @@
         <v>-0.6357</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9077</v>
+        <v>-0.9235</v>
       </c>
       <c r="E67" t="n">
         <v>-1.2038</v>
@@ -3538,7 +3538,7 @@
         <v>-0.6374</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9089</v>
+        <v>-0.9247</v>
       </c>
       <c r="E68" t="n">
         <v>-1.2069</v>
@@ -3584,7 +3584,7 @@
         <v>-0.6476</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9167</v>
+        <v>-0.9324</v>
       </c>
       <c r="E69" t="n">
         <v>-1.2262</v>
@@ -3620,93 +3620,93 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.2372</v>
+        <v>-1.2311</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.6534</v>
+        <v>-0.6501</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9212</v>
+        <v>-0.9344</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.2372</v>
+        <v>-1.2311</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.2372</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>-0.6116</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.2372</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.2372</v>
+        <v>-0.6353</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>-0.6116</v>
       </c>
       <c r="K70" t="n">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M70" t="n">
-        <v>-1.2372</v>
+        <v>-1.2469</v>
       </c>
       <c r="N70" t="n">
-        <v>202</v>
+        <v>242</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.2381</v>
+        <v>-1.2372</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.6538</v>
+        <v>-0.6534</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9215</v>
+        <v>-0.9368</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.2381</v>
+        <v>-1.2372</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.6264999999999999</v>
+        <v>-1.2372</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.6116</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.6264999999999999</v>
+        <v>-1.2372</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6353</v>
+        <v>-1.2372</v>
       </c>
       <c r="J71" t="n">
-        <v>-0.6116</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="L71" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-1.2469</v>
+        <v>-1.2372</v>
       </c>
       <c r="N71" t="n">
-        <v>242</v>
+        <v>202</v>
       </c>
     </row>
     <row r="72">
@@ -3722,7 +3722,7 @@
         <v>-0.6962</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.954</v>
+        <v>-0.9692</v>
       </c>
       <c r="E72" t="n">
         <v>-1.3184</v>
@@ -3762,25 +3762,25 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.5043</v>
+        <v>-1.4989</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.7944</v>
+        <v>-0.7916</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0291</v>
+        <v>-1.0411</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.5043</v>
+        <v>-1.4989</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.7202</v>
+        <v>-0.7148</v>
       </c>
       <c r="G73" t="n">
         <v>-0.7841</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.7202</v>
+        <v>-0.7148</v>
       </c>
       <c r="I73" t="n">
         <v>-0.7269</v>
@@ -3814,7 +3814,7 @@
         <v>-0.82</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0486</v>
+        <v>-1.0625</v>
       </c>
       <c r="E74" t="n">
         <v>-1.5527</v>
@@ -3860,7 +3860,7 @@
         <v>-0.8732</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0893</v>
+        <v>-1.1027</v>
       </c>
       <c r="E75" t="n">
         <v>-1.6535</v>
@@ -3906,7 +3906,7 @@
         <v>-0.8869</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0998</v>
+        <v>-1.113</v>
       </c>
       <c r="E76" t="n">
         <v>-1.6795</v>
@@ -3952,7 +3952,7 @@
         <v>-0.9291</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1321</v>
+        <v>-1.1448</v>
       </c>
       <c r="E77" t="n">
         <v>-1.7593</v>
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-2.1718</v>
+        <v>-2.163</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.1469</v>
+        <v>-1.1423</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.2987</v>
+        <v>-1.3056</v>
       </c>
       <c r="E78" t="n">
-        <v>-2.1718</v>
+        <v>-2.163</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.1718</v>
+        <v>-1.163</v>
       </c>
       <c r="G78" t="n">
         <v>-1</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.1718</v>
+        <v>-1.163</v>
       </c>
       <c r="I78" t="n">
         <v>-1.1827</v>
@@ -4044,7 +4044,7 @@
         <v>-1.4435</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.5256</v>
+        <v>-1.5329</v>
       </c>
       <c r="E79" t="n">
         <v>-2.7334</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-3.1049</v>
+        <v>-3.0818</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.6397</v>
+        <v>-1.6275</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.6757</v>
+        <v>-1.6717</v>
       </c>
       <c r="E80" t="n">
-        <v>-3.1049</v>
+        <v>-3.0818</v>
       </c>
       <c r="F80" t="n">
-        <v>-3.1049</v>
+        <v>-3.0818</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-3.1049</v>
+        <v>-3.0818</v>
       </c>
       <c r="I80" t="n">
         <v>-3.1339</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3.9995</v>
+        <v>-3.9661</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.1121</v>
+        <v>-2.0945</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.0371</v>
+        <v>-2.024</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.9995</v>
+        <v>-3.9661</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.9995</v>
+        <v>-2.9661</v>
       </c>
       <c r="G81" t="n">
         <v>-1</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.9995</v>
+        <v>-2.9661</v>
       </c>
       <c r="I81" t="n">
         <v>-3.0416</v>

--- a/database/event/8037/event_8037_evp_summary.xlsx
+++ b/database/event/8037/event_8037_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.345599999999999</v>
+        <v>8.5693</v>
       </c>
       <c r="C2" t="n">
-        <v>4.4073</v>
+        <v>4.5254</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1749</v>
+        <v>3.2139</v>
       </c>
       <c r="E2" t="n">
-        <v>8.345599999999999</v>
+        <v>8.5693</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6992</v>
+        <v>3.6986</v>
       </c>
       <c r="G2" t="n">
-        <v>4.6464</v>
+        <v>4.6467</v>
       </c>
       <c r="H2" t="n">
-        <v>7.3109</v>
+        <v>7.309</v>
       </c>
       <c r="I2" t="n">
-        <v>3.9478</v>
+        <v>3.9468</v>
       </c>
       <c r="J2" t="n">
-        <v>4.6464</v>
+        <v>4.6467</v>
       </c>
       <c r="K2" t="n">
         <v>154</v>
@@ -529,7 +529,7 @@
         <v>130</v>
       </c>
       <c r="M2" t="n">
-        <v>8.594200000000001</v>
+        <v>8.593500000000001</v>
       </c>
       <c r="N2" t="n">
         <v>284</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.0562</v>
+        <v>6.4753</v>
       </c>
       <c r="C3" t="n">
-        <v>3.1983</v>
+        <v>3.4196</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1327</v>
+        <v>2.2786</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0562</v>
+        <v>6.4753</v>
       </c>
       <c r="F3" t="n">
         <v>4.3271</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7291</v>
+        <v>1.7785</v>
       </c>
       <c r="H3" t="n">
-        <v>6.7458</v>
+        <v>6.7457</v>
       </c>
       <c r="I3" t="n">
-        <v>6.7458</v>
+        <v>6.7457</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7291</v>
+        <v>1.7785</v>
       </c>
       <c r="K3" t="n">
         <v>149</v>
@@ -575,7 +575,7 @@
         <v>127</v>
       </c>
       <c r="M3" t="n">
-        <v>8.4749</v>
+        <v>8.5242</v>
       </c>
       <c r="N3" t="n">
         <v>276</v>
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.7948</v>
+        <v>6.0075</v>
       </c>
       <c r="C4" t="n">
-        <v>3.0602</v>
+        <v>3.1725</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0137</v>
+        <v>2.0696</v>
       </c>
       <c r="E4" t="n">
-        <v>5.7948</v>
+        <v>6.0075</v>
       </c>
       <c r="F4" t="n">
         <v>4.5807</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2141</v>
+        <v>1.2125</v>
       </c>
       <c r="H4" t="n">
         <v>11.8593</v>
@@ -612,7 +612,7 @@
         <v>6.4039</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2141</v>
+        <v>1.2125</v>
       </c>
       <c r="K4" t="n">
         <v>125</v>
@@ -621,7 +621,7 @@
         <v>115</v>
       </c>
       <c r="M4" t="n">
-        <v>7.618</v>
+        <v>7.616400000000001</v>
       </c>
       <c r="N4" t="n">
         <v>240</v>
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.4816</v>
+        <v>5.872</v>
       </c>
       <c r="C5" t="n">
-        <v>2.8948</v>
+        <v>3.101</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8711</v>
+        <v>2.0091</v>
       </c>
       <c r="E5" t="n">
-        <v>5.4816</v>
+        <v>5.872</v>
       </c>
       <c r="F5" t="n">
         <v>4.5807</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9009</v>
+        <v>0.8995</v>
       </c>
       <c r="H5" t="n">
         <v>10.8272</v>
@@ -658,7 +658,7 @@
         <v>5.8466</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9009</v>
+        <v>0.8995</v>
       </c>
       <c r="K5" t="n">
         <v>125</v>
@@ -667,7 +667,7 @@
         <v>115</v>
       </c>
       <c r="M5" t="n">
-        <v>6.7475</v>
+        <v>6.746099999999999</v>
       </c>
       <c r="N5" t="n">
         <v>240</v>
@@ -676,35 +676,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.109</v>
+        <v>5.1449</v>
       </c>
       <c r="C6" t="n">
-        <v>2.698</v>
+        <v>2.717</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7015</v>
+        <v>1.6843</v>
       </c>
       <c r="E6" t="n">
-        <v>5.109</v>
+        <v>5.1449</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3432</v>
+        <v>3.7631</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7658</v>
+        <v>1.3319</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8369</v>
+        <v>7.5218</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5319</v>
+        <v>4.0617</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7658</v>
+        <v>1.3319</v>
       </c>
       <c r="K6" t="n">
         <v>154</v>
@@ -713,7 +713,7 @@
         <v>130</v>
       </c>
       <c r="M6" t="n">
-        <v>4.2977</v>
+        <v>5.3936</v>
       </c>
       <c r="N6" t="n">
         <v>284</v>
@@ -722,35 +722,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.081</v>
+        <v>5.106</v>
       </c>
       <c r="C7" t="n">
-        <v>2.6833</v>
+        <v>2.6965</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6888</v>
+        <v>1.6669</v>
       </c>
       <c r="E7" t="n">
-        <v>5.081</v>
+        <v>5.106</v>
       </c>
       <c r="F7" t="n">
-        <v>3.7494</v>
+        <v>2.3503</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3316</v>
+        <v>2.751</v>
       </c>
       <c r="H7" t="n">
-        <v>7.4764</v>
+        <v>2.8602</v>
       </c>
       <c r="I7" t="n">
-        <v>4.0372</v>
+        <v>1.5445</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3316</v>
+        <v>2.751</v>
       </c>
       <c r="K7" t="n">
         <v>154</v>
@@ -759,7 +759,7 @@
         <v>130</v>
       </c>
       <c r="M7" t="n">
-        <v>5.3688</v>
+        <v>4.2955</v>
       </c>
       <c r="N7" t="n">
         <v>284</v>
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.724</v>
+        <v>4.8306</v>
       </c>
       <c r="C8" t="n">
-        <v>2.4947</v>
+        <v>2.551</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5263</v>
+        <v>1.5439</v>
       </c>
       <c r="E8" t="n">
-        <v>4.724</v>
+        <v>4.8306</v>
       </c>
       <c r="F8" t="n">
         <v>2.6963</v>
       </c>
       <c r="G8" t="n">
-        <v>2.0277</v>
+        <v>2.0279</v>
       </c>
       <c r="H8" t="n">
         <v>3.1764</v>
@@ -796,7 +796,7 @@
         <v>3.2583</v>
       </c>
       <c r="J8" t="n">
-        <v>2.0277</v>
+        <v>2.0279</v>
       </c>
       <c r="K8" t="n">
         <v>144</v>
@@ -805,7 +805,7 @@
         <v>91</v>
       </c>
       <c r="M8" t="n">
-        <v>5.286</v>
+        <v>5.2862</v>
       </c>
       <c r="N8" t="n">
         <v>235</v>
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.5307</v>
+        <v>4.7725</v>
       </c>
       <c r="C9" t="n">
-        <v>2.3926</v>
+        <v>2.5203</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4383</v>
+        <v>1.518</v>
       </c>
       <c r="E9" t="n">
-        <v>4.5307</v>
+        <v>4.7725</v>
       </c>
       <c r="F9" t="n">
         <v>4.1197</v>
@@ -864,22 +864,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.229</v>
+        <v>4.4787</v>
       </c>
       <c r="C10" t="n">
-        <v>2.2333</v>
+        <v>2.3652</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3009</v>
+        <v>1.3867</v>
       </c>
       <c r="E10" t="n">
-        <v>4.229</v>
+        <v>4.4787</v>
       </c>
       <c r="F10" t="n">
         <v>2.9609</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2681</v>
+        <v>1.2685</v>
       </c>
       <c r="H10" t="n">
         <v>3.7556</v>
@@ -888,7 +888,7 @@
         <v>3.8524</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2681</v>
+        <v>1.2685</v>
       </c>
       <c r="K10" t="n">
         <v>144</v>
@@ -897,7 +897,7 @@
         <v>91</v>
       </c>
       <c r="M10" t="n">
-        <v>5.1205</v>
+        <v>5.1209</v>
       </c>
       <c r="N10" t="n">
         <v>235</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>HeavyGod</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.1342</v>
+        <v>4.319</v>
       </c>
       <c r="C11" t="n">
-        <v>2.1833</v>
+        <v>2.2808</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2578</v>
+        <v>1.3154</v>
       </c>
       <c r="E11" t="n">
-        <v>4.1342</v>
+        <v>4.319</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5023</v>
+        <v>4.0366</v>
       </c>
       <c r="G11" t="n">
-        <v>2.6319</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5023</v>
+        <v>6.1099</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5023</v>
+        <v>6.2673</v>
       </c>
       <c r="J11" t="n">
-        <v>2.6319</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>149</v>
+        <v>209</v>
       </c>
       <c r="L11" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.1342</v>
+        <v>6.2673</v>
       </c>
       <c r="N11" t="n">
-        <v>276</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HeavyGod</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.0364</v>
+        <v>4.2808</v>
       </c>
       <c r="C12" t="n">
-        <v>2.1316</v>
+        <v>2.2607</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2132</v>
+        <v>1.2983</v>
       </c>
       <c r="E12" t="n">
-        <v>4.0364</v>
+        <v>4.2808</v>
       </c>
       <c r="F12" t="n">
-        <v>4.0364</v>
+        <v>1.5292</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2.6413</v>
       </c>
       <c r="H12" t="n">
-        <v>6.1094</v>
+        <v>1.5292</v>
       </c>
       <c r="I12" t="n">
-        <v>6.2668</v>
+        <v>1.5292</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>2.6413</v>
       </c>
       <c r="K12" t="n">
-        <v>209</v>
+        <v>149</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="M12" t="n">
-        <v>6.2668</v>
+        <v>4.170500000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>209</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13">
@@ -1002,16 +1002,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.0025</v>
+        <v>4.2251</v>
       </c>
       <c r="C13" t="n">
-        <v>2.1137</v>
+        <v>2.2313</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1978</v>
+        <v>1.2734</v>
       </c>
       <c r="E13" t="n">
-        <v>4.0025</v>
+        <v>4.2251</v>
       </c>
       <c r="F13" t="n">
         <v>3.2443</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.6669</v>
+        <v>3.8991</v>
       </c>
       <c r="C14" t="n">
-        <v>1.9365</v>
+        <v>2.0591</v>
       </c>
       <c r="D14" t="n">
-        <v>1.045</v>
+        <v>1.1278</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6669</v>
+        <v>3.8991</v>
       </c>
       <c r="F14" t="n">
-        <v>3.6669</v>
+        <v>3.6672</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>5.3007</v>
+        <v>5.3014</v>
       </c>
       <c r="I14" t="n">
-        <v>5.5774</v>
+        <v>5.5781</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>5.5774</v>
+        <v>5.5781</v>
       </c>
       <c r="N14" t="n">
         <v>262</v>
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.5701</v>
+        <v>3.8125</v>
       </c>
       <c r="C15" t="n">
-        <v>1.8854</v>
+        <v>2.0134</v>
       </c>
       <c r="D15" t="n">
-        <v>1.001</v>
+        <v>1.0891</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5701</v>
+        <v>3.8125</v>
       </c>
       <c r="F15" t="n">
         <v>3.7589</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.5391</v>
+        <v>3.7105</v>
       </c>
       <c r="C16" t="n">
-        <v>1.869</v>
+        <v>1.9595</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9869</v>
+        <v>1.0436</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5391</v>
+        <v>3.7105</v>
       </c>
       <c r="F16" t="n">
-        <v>3.5391</v>
+        <v>3.5396</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>5.0211</v>
+        <v>5.0221</v>
       </c>
       <c r="I16" t="n">
-        <v>5.2832</v>
+        <v>5.2843</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>5.2832</v>
+        <v>5.2843</v>
       </c>
       <c r="N16" t="n">
         <v>262</v>
@@ -1186,22 +1186,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.3224</v>
+        <v>3.3263</v>
       </c>
       <c r="C17" t="n">
-        <v>1.7545</v>
+        <v>1.7566</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8882</v>
+        <v>0.872</v>
       </c>
       <c r="E17" t="n">
-        <v>3.3224</v>
+        <v>3.3263</v>
       </c>
       <c r="F17" t="n">
         <v>3.7411</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4187</v>
+        <v>-0.3845</v>
       </c>
       <c r="H17" t="n">
         <v>7.4492</v>
@@ -1210,7 +1210,7 @@
         <v>4.0225</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4187</v>
+        <v>-0.3845</v>
       </c>
       <c r="K17" t="n">
         <v>125</v>
@@ -1219,7 +1219,7 @@
         <v>115</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6038</v>
+        <v>3.638</v>
       </c>
       <c r="N17" t="n">
         <v>240</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.1966</v>
+        <v>3.1332</v>
       </c>
       <c r="C18" t="n">
-        <v>1.6881</v>
+        <v>1.6546</v>
       </c>
       <c r="D18" t="n">
-        <v>0.831</v>
+        <v>0.7857</v>
       </c>
       <c r="E18" t="n">
-        <v>3.1966</v>
+        <v>3.1332</v>
       </c>
       <c r="F18" t="n">
-        <v>2.9916</v>
+        <v>2.9914</v>
       </c>
       <c r="G18" t="n">
-        <v>0.205</v>
+        <v>0.2053</v>
       </c>
       <c r="H18" t="n">
-        <v>4.9764</v>
+        <v>4.9754</v>
       </c>
       <c r="I18" t="n">
-        <v>2.6872</v>
+        <v>2.6867</v>
       </c>
       <c r="J18" t="n">
-        <v>0.205</v>
+        <v>0.2053</v>
       </c>
       <c r="K18" t="n">
         <v>154</v>
@@ -1265,7 +1265,7 @@
         <v>130</v>
       </c>
       <c r="M18" t="n">
-        <v>2.8922</v>
+        <v>2.892</v>
       </c>
       <c r="N18" t="n">
         <v>284</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.9098</v>
+        <v>3.0606</v>
       </c>
       <c r="C19" t="n">
-        <v>1.5367</v>
+        <v>1.6163</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7004</v>
+        <v>0.7533</v>
       </c>
       <c r="E19" t="n">
-        <v>2.9098</v>
+        <v>3.0606</v>
       </c>
       <c r="F19" t="n">
-        <v>2.9098</v>
+        <v>2.8926</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>3.6438</v>
+        <v>3.6061</v>
       </c>
       <c r="I19" t="n">
-        <v>3.834</v>
+        <v>3.7943</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.834</v>
+        <v>3.7943</v>
       </c>
       <c r="N19" t="n">
         <v>262</v>
@@ -1324,22 +1324,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.8643</v>
+        <v>2.9421</v>
       </c>
       <c r="C20" t="n">
-        <v>1.5126</v>
+        <v>1.5537</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6797</v>
+        <v>0.7004</v>
       </c>
       <c r="E20" t="n">
-        <v>2.8643</v>
+        <v>2.9421</v>
       </c>
       <c r="F20" t="n">
         <v>2.129</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7353</v>
+        <v>0.7788</v>
       </c>
       <c r="H20" t="n">
         <v>2.13</v>
@@ -1348,7 +1348,7 @@
         <v>1.1502</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7353</v>
+        <v>0.7788</v>
       </c>
       <c r="K20" t="n">
         <v>125</v>
@@ -1357,7 +1357,7 @@
         <v>115</v>
       </c>
       <c r="M20" t="n">
-        <v>1.8855</v>
+        <v>1.929</v>
       </c>
       <c r="N20" t="n">
         <v>240</v>
@@ -1366,277 +1366,277 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>molodoy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.8417</v>
+        <v>2.8774</v>
       </c>
       <c r="C21" t="n">
-        <v>1.5007</v>
+        <v>1.5195</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6694</v>
+        <v>0.6715</v>
       </c>
       <c r="E21" t="n">
-        <v>2.8417</v>
+        <v>2.8774</v>
       </c>
       <c r="F21" t="n">
-        <v>2.5219</v>
+        <v>2.5454</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3198</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.7947</v>
+        <v>2.8461</v>
       </c>
       <c r="I21" t="n">
-        <v>2.9406</v>
+        <v>2.8461</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3198</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>240</v>
+        <v>144</v>
       </c>
       <c r="L21" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2604</v>
+        <v>2.8461</v>
       </c>
       <c r="N21" t="n">
-        <v>304</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.7392</v>
+        <v>2.8413</v>
       </c>
       <c r="C22" t="n">
-        <v>1.4466</v>
+        <v>1.5005</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6227</v>
+        <v>0.6553</v>
       </c>
       <c r="E22" t="n">
-        <v>2.7392</v>
+        <v>2.8413</v>
       </c>
       <c r="F22" t="n">
-        <v>2.113</v>
+        <v>2.5139</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6262</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.113</v>
+        <v>2.7771</v>
       </c>
       <c r="I22" t="n">
-        <v>2.1674</v>
+        <v>2.7771</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6262</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="L22" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.7936</v>
+        <v>2.7771</v>
       </c>
       <c r="N22" t="n">
-        <v>235</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>molodoy</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.5452</v>
+        <v>2.8091</v>
       </c>
       <c r="C23" t="n">
-        <v>1.3441</v>
+        <v>1.4835</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5344</v>
+        <v>0.6409</v>
       </c>
       <c r="E23" t="n">
-        <v>2.5452</v>
+        <v>2.8091</v>
       </c>
       <c r="F23" t="n">
-        <v>2.5452</v>
+        <v>2.113</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.6264</v>
       </c>
       <c r="H23" t="n">
-        <v>2.8458</v>
+        <v>2.113</v>
       </c>
       <c r="I23" t="n">
-        <v>2.8458</v>
+        <v>2.1674</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.6264</v>
       </c>
       <c r="K23" t="n">
         <v>144</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="M23" t="n">
-        <v>2.8458</v>
+        <v>2.7938</v>
       </c>
       <c r="N23" t="n">
-        <v>144</v>
+        <v>235</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.5203</v>
+        <v>2.7552</v>
       </c>
       <c r="C24" t="n">
-        <v>1.331</v>
+        <v>1.455</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5231</v>
+        <v>0.6169</v>
       </c>
       <c r="E24" t="n">
-        <v>2.5203</v>
+        <v>2.7552</v>
       </c>
       <c r="F24" t="n">
-        <v>2.5203</v>
+        <v>2.5276</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.2643</v>
       </c>
       <c r="H24" t="n">
-        <v>2.7913</v>
+        <v>2.8073</v>
       </c>
       <c r="I24" t="n">
-        <v>2.7913</v>
+        <v>2.9538</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.2643</v>
       </c>
       <c r="K24" t="n">
-        <v>124</v>
+        <v>240</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M24" t="n">
-        <v>2.7913</v>
+        <v>3.2181</v>
       </c>
       <c r="N24" t="n">
-        <v>124</v>
+        <v>304</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.466</v>
+        <v>2.6273</v>
       </c>
       <c r="C25" t="n">
-        <v>1.3023</v>
+        <v>1.3875</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4984</v>
+        <v>0.5597</v>
       </c>
       <c r="E25" t="n">
-        <v>2.466</v>
+        <v>2.6273</v>
       </c>
       <c r="F25" t="n">
-        <v>1.5594</v>
+        <v>2.4556</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9066</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.5594</v>
+        <v>2.6495</v>
       </c>
       <c r="I25" t="n">
-        <v>1.6408</v>
+        <v>2.6495</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9066</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>240</v>
+        <v>144</v>
       </c>
       <c r="L25" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.5474</v>
+        <v>2.6495</v>
       </c>
       <c r="N25" t="n">
-        <v>304</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.4555</v>
+        <v>2.5354</v>
       </c>
       <c r="C26" t="n">
-        <v>1.2967</v>
+        <v>1.3389</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4936</v>
+        <v>0.5187</v>
       </c>
       <c r="E26" t="n">
-        <v>2.4555</v>
+        <v>2.5354</v>
       </c>
       <c r="F26" t="n">
-        <v>2.4555</v>
+        <v>2.3246</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2.6494</v>
+        <v>2.3628</v>
       </c>
       <c r="I26" t="n">
-        <v>2.6494</v>
+        <v>2.3628</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.6494</v>
+        <v>2.3628</v>
       </c>
       <c r="N26" t="n">
-        <v>144</v>
+        <v>158</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.3736</v>
+        <v>2.4564</v>
       </c>
       <c r="C27" t="n">
-        <v>1.2535</v>
+        <v>1.2972</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4563</v>
+        <v>0.4834</v>
       </c>
       <c r="E27" t="n">
-        <v>2.3736</v>
+        <v>2.4564</v>
       </c>
       <c r="F27" t="n">
-        <v>2.3736</v>
+        <v>2.3664</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>2.4701</v>
+        <v>2.4544</v>
       </c>
       <c r="I27" t="n">
-        <v>2.4701</v>
+        <v>2.4544</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2.4701</v>
+        <v>2.4544</v>
       </c>
       <c r="N27" t="n">
         <v>202</v>
@@ -1688,78 +1688,78 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.3363</v>
+        <v>2.453</v>
       </c>
       <c r="C28" t="n">
-        <v>1.2338</v>
+        <v>1.2954</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4393</v>
+        <v>0.4819</v>
       </c>
       <c r="E28" t="n">
-        <v>2.3363</v>
+        <v>2.453</v>
       </c>
       <c r="F28" t="n">
-        <v>2.3363</v>
+        <v>1.5705</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.8981</v>
       </c>
       <c r="H28" t="n">
-        <v>2.3885</v>
+        <v>1.5705</v>
       </c>
       <c r="I28" t="n">
-        <v>2.45</v>
+        <v>1.6525</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.8981</v>
       </c>
       <c r="K28" t="n">
-        <v>209</v>
+        <v>240</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M28" t="n">
-        <v>2.45</v>
+        <v>2.5506</v>
       </c>
       <c r="N28" t="n">
-        <v>209</v>
+        <v>304</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.3252</v>
+        <v>2.4114</v>
       </c>
       <c r="C29" t="n">
-        <v>1.2279</v>
+        <v>1.2734</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4343</v>
+        <v>0.4633</v>
       </c>
       <c r="E29" t="n">
-        <v>2.3252</v>
+        <v>2.4114</v>
       </c>
       <c r="F29" t="n">
-        <v>2.3252</v>
+        <v>2.1911</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2.3643</v>
+        <v>2.1911</v>
       </c>
       <c r="I29" t="n">
-        <v>2.3643</v>
+        <v>2.1911</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2.3643</v>
+        <v>2.1911</v>
       </c>
       <c r="N29" t="n">
         <v>158</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.2992</v>
+        <v>2.4069</v>
       </c>
       <c r="C30" t="n">
-        <v>1.2142</v>
+        <v>1.2711</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4224</v>
+        <v>0.4613</v>
       </c>
       <c r="E30" t="n">
-        <v>2.2992</v>
+        <v>2.4069</v>
       </c>
       <c r="F30" t="n">
-        <v>2.2992</v>
+        <v>2.2993</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>2.3074</v>
+        <v>2.3076</v>
       </c>
       <c r="I30" t="n">
-        <v>2.3074</v>
+        <v>2.3076</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>2.3074</v>
+        <v>2.3076</v>
       </c>
       <c r="N30" t="n">
         <v>202</v>
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.2907</v>
+        <v>2.3178</v>
       </c>
       <c r="C31" t="n">
-        <v>1.2097</v>
+        <v>1.224</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4186</v>
+        <v>0.4215</v>
       </c>
       <c r="E31" t="n">
-        <v>2.2907</v>
+        <v>2.3178</v>
       </c>
       <c r="F31" t="n">
-        <v>2.8276</v>
+        <v>2.8183</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.5369</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>3.4637</v>
+        <v>3.4434</v>
       </c>
       <c r="I31" t="n">
-        <v>3.6445</v>
+        <v>3.6231</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.5369</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="K31" t="n">
         <v>240</v>
@@ -1863,7 +1863,7 @@
         <v>64</v>
       </c>
       <c r="M31" t="n">
-        <v>3.1076</v>
+        <v>3.0893</v>
       </c>
       <c r="N31" t="n">
         <v>304</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.2837</v>
+        <v>2.3102</v>
       </c>
       <c r="C32" t="n">
-        <v>1.206</v>
+        <v>1.22</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4154</v>
+        <v>0.4181</v>
       </c>
       <c r="E32" t="n">
-        <v>2.2837</v>
+        <v>2.3102</v>
       </c>
       <c r="F32" t="n">
-        <v>1.4338</v>
+        <v>2.3223</v>
       </c>
       <c r="G32" t="n">
-        <v>0.8499</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.4338</v>
+        <v>2.3578</v>
       </c>
       <c r="I32" t="n">
-        <v>1.4707</v>
+        <v>2.4186</v>
       </c>
       <c r="J32" t="n">
-        <v>0.8499</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>144</v>
+        <v>209</v>
       </c>
       <c r="L32" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2.3206</v>
+        <v>2.4186</v>
       </c>
       <c r="N32" t="n">
-        <v>235</v>
+        <v>209</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.1708</v>
+        <v>2.2694</v>
       </c>
       <c r="C33" t="n">
-        <v>1.1464</v>
+        <v>1.1985</v>
       </c>
       <c r="D33" t="n">
-        <v>0.364</v>
+        <v>0.3999</v>
       </c>
       <c r="E33" t="n">
-        <v>2.1708</v>
+        <v>2.2694</v>
       </c>
       <c r="F33" t="n">
-        <v>2.1708</v>
+        <v>1.4338</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.8502</v>
       </c>
       <c r="H33" t="n">
-        <v>2.1708</v>
+        <v>1.4338</v>
       </c>
       <c r="I33" t="n">
-        <v>2.1708</v>
+        <v>1.4707</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.8502</v>
       </c>
       <c r="K33" t="n">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="M33" t="n">
-        <v>2.1708</v>
+        <v>2.3209</v>
       </c>
       <c r="N33" t="n">
-        <v>158</v>
+        <v>235</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.0123</v>
+        <v>2.0038</v>
       </c>
       <c r="C34" t="n">
-        <v>1.0627</v>
+        <v>1.0582</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2918</v>
+        <v>0.2812</v>
       </c>
       <c r="E34" t="n">
-        <v>2.0123</v>
+        <v>2.0038</v>
       </c>
       <c r="F34" t="n">
-        <v>2.0123</v>
+        <v>2.0124</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2.0123</v>
+        <v>2.0124</v>
       </c>
       <c r="I34" t="n">
-        <v>2.0123</v>
+        <v>2.0124</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>2.0123</v>
+        <v>2.0124</v>
       </c>
       <c r="N34" t="n">
         <v>144</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.9178</v>
+        <v>1.9847</v>
       </c>
       <c r="C35" t="n">
-        <v>1.0128</v>
+        <v>1.0481</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2488</v>
+        <v>0.2727</v>
       </c>
       <c r="E35" t="n">
-        <v>1.9178</v>
+        <v>1.9847</v>
       </c>
       <c r="F35" t="n">
-        <v>1.9178</v>
+        <v>1.9175</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.9178</v>
+        <v>1.9175</v>
       </c>
       <c r="I35" t="n">
-        <v>1.9178</v>
+        <v>1.9175</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.9178</v>
+        <v>1.9175</v>
       </c>
       <c r="N35" t="n">
         <v>158</v>
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.8885</v>
+        <v>1.8209</v>
       </c>
       <c r="C36" t="n">
-        <v>0.9973</v>
+        <v>0.9616</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2355</v>
+        <v>0.1995</v>
       </c>
       <c r="E36" t="n">
-        <v>1.8885</v>
+        <v>1.8209</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.0794</v>
+        <v>-0.1038</v>
       </c>
       <c r="G36" t="n">
-        <v>1.9679</v>
+        <v>1.9788</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.0794</v>
+        <v>-0.1038</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.0794</v>
+        <v>-0.1038</v>
       </c>
       <c r="J36" t="n">
-        <v>1.9679</v>
+        <v>1.9788</v>
       </c>
       <c r="K36" t="n">
         <v>149</v>
@@ -2093,7 +2093,7 @@
         <v>127</v>
       </c>
       <c r="M36" t="n">
-        <v>1.8885</v>
+        <v>1.875</v>
       </c>
       <c r="N36" t="n">
         <v>276</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.7405</v>
+        <v>1.7687</v>
       </c>
       <c r="C37" t="n">
-        <v>0.9192</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1681</v>
+        <v>0.1762</v>
       </c>
       <c r="E37" t="n">
-        <v>1.7405</v>
+        <v>1.7687</v>
       </c>
       <c r="F37" t="n">
-        <v>1.7405</v>
+        <v>1.7396</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.7405</v>
+        <v>1.7396</v>
       </c>
       <c r="I37" t="n">
-        <v>1.7405</v>
+        <v>1.7396</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.7405</v>
+        <v>1.7396</v>
       </c>
       <c r="N37" t="n">
         <v>120</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.712</v>
+        <v>1.721</v>
       </c>
       <c r="C38" t="n">
-        <v>0.9041</v>
+        <v>0.9089</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1551</v>
+        <v>0.1549</v>
       </c>
       <c r="E38" t="n">
-        <v>1.712</v>
+        <v>1.721</v>
       </c>
       <c r="F38" t="n">
-        <v>1.712</v>
+        <v>1.7123</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.712</v>
+        <v>1.7123</v>
       </c>
       <c r="I38" t="n">
-        <v>1.7561</v>
+        <v>1.7564</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1.7561</v>
+        <v>1.7564</v>
       </c>
       <c r="N38" t="n">
         <v>209</v>
@@ -2194,93 +2194,93 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>Starry</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.5422</v>
+        <v>1.7112</v>
       </c>
       <c r="C39" t="n">
-        <v>0.8144</v>
+        <v>0.9036999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.1505</v>
       </c>
       <c r="E39" t="n">
-        <v>1.5422</v>
+        <v>1.7112</v>
       </c>
       <c r="F39" t="n">
-        <v>1.5422</v>
+        <v>1.2619</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.5422</v>
+        <v>1.2619</v>
       </c>
       <c r="I39" t="n">
-        <v>1.5422</v>
+        <v>1.2619</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1.5422</v>
+        <v>1.2619</v>
       </c>
       <c r="N39" t="n">
-        <v>158</v>
+        <v>83</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.5388</v>
+        <v>1.569</v>
       </c>
       <c r="C40" t="n">
-        <v>0.8126</v>
+        <v>0.8286</v>
       </c>
       <c r="D40" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>1.5388</v>
+        <v>1.569</v>
       </c>
       <c r="F40" t="n">
-        <v>1.962</v>
+        <v>1.5419</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.4232</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.962</v>
+        <v>1.5419</v>
       </c>
       <c r="I40" t="n">
-        <v>2.0126</v>
+        <v>1.5419</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.4232</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="L40" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.5894</v>
+        <v>1.5419</v>
       </c>
       <c r="N40" t="n">
-        <v>235</v>
+        <v>158</v>
       </c>
     </row>
     <row r="41">
@@ -2290,22 +2290,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.5292</v>
+        <v>1.4238</v>
       </c>
       <c r="C41" t="n">
-        <v>0.8076</v>
+        <v>0.7519</v>
       </c>
       <c r="D41" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0222</v>
       </c>
       <c r="E41" t="n">
-        <v>1.5292</v>
+        <v>1.4238</v>
       </c>
       <c r="F41" t="n">
         <v>2.4151</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.8859</v>
+        <v>-0.8871</v>
       </c>
       <c r="H41" t="n">
         <v>3.0741</v>
@@ -2314,7 +2314,7 @@
         <v>1.66</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.8859</v>
+        <v>-0.8871</v>
       </c>
       <c r="K41" t="n">
         <v>125</v>
@@ -2323,7 +2323,7 @@
         <v>115</v>
       </c>
       <c r="M41" t="n">
-        <v>0.7740999999999999</v>
+        <v>0.7728999999999999</v>
       </c>
       <c r="N41" t="n">
         <v>240</v>
@@ -2332,277 +2332,277 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>hades</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.3394</v>
+        <v>1.3369</v>
       </c>
       <c r="C42" t="n">
-        <v>0.7073</v>
+        <v>0.706</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.0145</v>
+        <v>-0.0167</v>
       </c>
       <c r="E42" t="n">
-        <v>1.3394</v>
+        <v>1.3369</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0728</v>
+        <v>1.3074</v>
       </c>
       <c r="G42" t="n">
-        <v>1.2666</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0728</v>
+        <v>1.3074</v>
       </c>
       <c r="I42" t="n">
-        <v>0.0728</v>
+        <v>1.3411</v>
       </c>
       <c r="J42" t="n">
-        <v>1.2666</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>149</v>
+        <v>209</v>
       </c>
       <c r="L42" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1.3394</v>
+        <v>1.3411</v>
       </c>
       <c r="N42" t="n">
-        <v>276</v>
+        <v>209</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>hades</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.3072</v>
+        <v>1.3262</v>
       </c>
       <c r="C43" t="n">
-        <v>0.6903</v>
+        <v>0.7004</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.0291</v>
+        <v>-0.0214</v>
       </c>
       <c r="E43" t="n">
-        <v>1.3072</v>
+        <v>1.3262</v>
       </c>
       <c r="F43" t="n">
-        <v>1.3072</v>
+        <v>1.962</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>-0.4343</v>
       </c>
       <c r="H43" t="n">
-        <v>1.3072</v>
+        <v>1.962</v>
       </c>
       <c r="I43" t="n">
-        <v>1.3409</v>
+        <v>2.0126</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>-0.4343</v>
       </c>
       <c r="K43" t="n">
-        <v>209</v>
+        <v>144</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="M43" t="n">
-        <v>1.3409</v>
+        <v>1.5783</v>
       </c>
       <c r="N43" t="n">
-        <v>209</v>
+        <v>235</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.2941</v>
+        <v>1.234</v>
       </c>
       <c r="C44" t="n">
-        <v>0.6834</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.0351</v>
+        <v>-0.0626</v>
       </c>
       <c r="E44" t="n">
-        <v>1.2941</v>
+        <v>1.234</v>
       </c>
       <c r="F44" t="n">
-        <v>2.1471</v>
+        <v>0.0728</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.853</v>
+        <v>1.3238</v>
       </c>
       <c r="H44" t="n">
-        <v>2.1898</v>
+        <v>0.0728</v>
       </c>
       <c r="I44" t="n">
-        <v>1.1825</v>
+        <v>0.0728</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.853</v>
+        <v>1.3238</v>
       </c>
       <c r="K44" t="n">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="L44" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="M44" t="n">
-        <v>0.3295000000000001</v>
+        <v>1.3966</v>
       </c>
       <c r="N44" t="n">
-        <v>284</v>
+        <v>276</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Starry</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.2619</v>
+        <v>1.2051</v>
       </c>
       <c r="C45" t="n">
-        <v>0.6664</v>
+        <v>0.6364</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.0498</v>
+        <v>-0.0755</v>
       </c>
       <c r="E45" t="n">
-        <v>1.2619</v>
+        <v>1.2051</v>
       </c>
       <c r="F45" t="n">
-        <v>1.2619</v>
+        <v>2.1468</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>-0.8527</v>
       </c>
       <c r="H45" t="n">
-        <v>1.2619</v>
+        <v>2.1887</v>
       </c>
       <c r="I45" t="n">
-        <v>1.2619</v>
+        <v>1.1819</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>-0.8527</v>
       </c>
       <c r="K45" t="n">
-        <v>83</v>
+        <v>154</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="M45" t="n">
-        <v>1.2619</v>
+        <v>0.3291999999999999</v>
       </c>
       <c r="N45" t="n">
-        <v>83</v>
+        <v>284</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.0512</v>
+        <v>1.0418</v>
       </c>
       <c r="C46" t="n">
-        <v>0.5551</v>
+        <v>0.5502</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.1457</v>
+        <v>-0.1485</v>
       </c>
       <c r="E46" t="n">
-        <v>1.0512</v>
+        <v>1.0418</v>
       </c>
       <c r="F46" t="n">
-        <v>1.0512</v>
+        <v>1.0151</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1.0512</v>
+        <v>1.0151</v>
       </c>
       <c r="I46" t="n">
-        <v>1.0512</v>
+        <v>1.0151</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>202</v>
+        <v>124</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1.0512</v>
+        <v>1.0151</v>
       </c>
       <c r="N46" t="n">
-        <v>202</v>
+        <v>124</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.0151</v>
+        <v>0.9989</v>
       </c>
       <c r="C47" t="n">
-        <v>0.5361</v>
+        <v>0.5275</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.1621</v>
+        <v>-0.1676</v>
       </c>
       <c r="E47" t="n">
-        <v>1.0151</v>
+        <v>0.9989</v>
       </c>
       <c r="F47" t="n">
-        <v>1.0151</v>
+        <v>1.0512</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>1.0151</v>
+        <v>1.0512</v>
       </c>
       <c r="I47" t="n">
-        <v>1.0151</v>
+        <v>1.0512</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>124</v>
+        <v>202</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>1.0151</v>
+        <v>1.0512</v>
       </c>
       <c r="N47" t="n">
-        <v>124</v>
+        <v>202</v>
       </c>
     </row>
     <row r="48">
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.9961</v>
+        <v>0.9003</v>
       </c>
       <c r="C48" t="n">
-        <v>0.526</v>
+        <v>0.4754</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.1708</v>
+        <v>-0.2117</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9961</v>
+        <v>0.9003</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9961</v>
+        <v>0.9969</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.9961</v>
+        <v>0.9969</v>
       </c>
       <c r="I48" t="n">
-        <v>1.0481</v>
+        <v>1.0489</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>1.0481</v>
+        <v>1.0489</v>
       </c>
       <c r="N48" t="n">
         <v>262</v>
@@ -2654,93 +2654,93 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>latto</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.575</v>
+        <v>0.6008</v>
       </c>
       <c r="C49" t="n">
-        <v>0.3037</v>
+        <v>0.3173</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3625</v>
+        <v>-0.3455</v>
       </c>
       <c r="E49" t="n">
-        <v>0.575</v>
+        <v>0.6008</v>
       </c>
       <c r="F49" t="n">
-        <v>0.575</v>
+        <v>0.5327</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.575</v>
+        <v>0.5327</v>
       </c>
       <c r="I49" t="n">
-        <v>0.575</v>
+        <v>0.5327</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.575</v>
+        <v>0.5327</v>
       </c>
       <c r="N49" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>latto</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5336</v>
+        <v>0.4691</v>
       </c>
       <c r="C50" t="n">
-        <v>0.2818</v>
+        <v>0.2477</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3813</v>
+        <v>-0.4043</v>
       </c>
       <c r="E50" t="n">
-        <v>0.5336</v>
+        <v>0.4691</v>
       </c>
       <c r="F50" t="n">
-        <v>0.5336</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.5336</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>0.5336</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.5336</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="N50" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="51">
@@ -2750,28 +2750,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5188</v>
+        <v>0.355</v>
       </c>
       <c r="C51" t="n">
-        <v>0.274</v>
+        <v>0.1875</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.388</v>
+        <v>-0.4552</v>
       </c>
       <c r="E51" t="n">
-        <v>0.5188</v>
+        <v>0.355</v>
       </c>
       <c r="F51" t="n">
-        <v>0.5188</v>
+        <v>0.5191</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.5188</v>
+        <v>0.5191</v>
       </c>
       <c r="I51" t="n">
-        <v>0.5322</v>
+        <v>0.5325</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.5322</v>
+        <v>0.5325</v>
       </c>
       <c r="N51" t="n">
         <v>209</v>
@@ -2792,93 +2792,93 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.3614</v>
+        <v>0.2513</v>
       </c>
       <c r="C52" t="n">
-        <v>0.1909</v>
+        <v>0.1327</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4597</v>
+        <v>-0.5016</v>
       </c>
       <c r="E52" t="n">
-        <v>0.3614</v>
+        <v>0.2513</v>
       </c>
       <c r="F52" t="n">
-        <v>0.4665</v>
+        <v>0.3423</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.1051</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.4665</v>
+        <v>0.3423</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4665</v>
+        <v>0.3423</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.1051</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>149</v>
+        <v>83</v>
       </c>
       <c r="L52" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.3614000000000001</v>
+        <v>0.3423</v>
       </c>
       <c r="N52" t="n">
-        <v>276</v>
+        <v>83</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.3423</v>
+        <v>0.1846</v>
       </c>
       <c r="C53" t="n">
-        <v>0.1808</v>
+        <v>0.0975</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4684</v>
+        <v>-0.5314</v>
       </c>
       <c r="E53" t="n">
-        <v>0.3423</v>
+        <v>0.1846</v>
       </c>
       <c r="F53" t="n">
-        <v>0.3423</v>
+        <v>0.4663</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>-0.0891</v>
       </c>
       <c r="H53" t="n">
-        <v>0.3423</v>
+        <v>0.4663</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3423</v>
+        <v>0.4663</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>-0.0891</v>
       </c>
       <c r="K53" t="n">
-        <v>83</v>
+        <v>149</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="M53" t="n">
-        <v>0.3423</v>
+        <v>0.3772</v>
       </c>
       <c r="N53" t="n">
-        <v>83</v>
+        <v>276</v>
       </c>
     </row>
     <row r="54">
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.012</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.0063</v>
+        <v>0.0411</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.6297</v>
+        <v>-0.5790999999999999</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.012</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.012</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.012</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.012</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.012</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="N54" t="n">
         <v>120</v>
@@ -2930,231 +2930,231 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>CYPHER</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0196</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.0357</v>
+        <v>-0.0104</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.655</v>
+        <v>-0.6226</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0196</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.3219</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.3219</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.3219</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>144</v>
+        <v>84</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.3219</v>
       </c>
       <c r="N55" t="n">
-        <v>144</v>
+        <v>84</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>dumau</t>
+          <t>nawwk</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.0693</v>
+        <v>-0.031</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.0366</v>
+        <v>-0.0164</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6558</v>
+        <v>-0.6277</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.0693</v>
+        <v>-0.031</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.0693</v>
+        <v>-0.1351</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.0693</v>
+        <v>-0.1351</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.0693</v>
+        <v>-0.1351</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.0693</v>
+        <v>-0.1351</v>
       </c>
       <c r="N56" t="n">
-        <v>120</v>
+        <v>84</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>nawwk</t>
+          <t>dumau</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.1553</v>
+        <v>-0.1128</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.082</v>
+        <v>-0.0596</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6949</v>
+        <v>-0.6642</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.1553</v>
+        <v>-0.1128</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.1553</v>
+        <v>-0.0528</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.1553</v>
+        <v>-0.0528</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.1553</v>
+        <v>-0.0528</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.1553</v>
+        <v>-0.0528</v>
       </c>
       <c r="N57" t="n">
-        <v>84</v>
+        <v>120</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Westmelon</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.2194</v>
+        <v>-0.2059</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.1159</v>
+        <v>-0.1087</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.7241</v>
+        <v>-0.7058</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.2194</v>
+        <v>-0.2059</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.2194</v>
+        <v>-0.0675</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.2194</v>
+        <v>-0.0675</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.2194</v>
+        <v>-0.0675</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>83</v>
+        <v>144</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.2194</v>
+        <v>-0.0675</v>
       </c>
       <c r="N58" t="n">
-        <v>83</v>
+        <v>144</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>pr1metapz</t>
+          <t>oSee</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.2204</v>
+        <v>-0.2895</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.1164</v>
+        <v>-0.1529</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.7245</v>
+        <v>-0.7431</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.2204</v>
+        <v>-0.2895</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.2204</v>
+        <v>-0.3181</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.2204</v>
+        <v>-0.3181</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2204</v>
+        <v>-0.3181</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.2204</v>
+        <v>-0.3181</v>
       </c>
       <c r="N59" t="n">
-        <v>84</v>
+        <v>71</v>
       </c>
     </row>
     <row r="60">
@@ -3164,16 +3164,16 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.2688</v>
+        <v>-0.3025</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.142</v>
+        <v>-0.1597</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7466</v>
+        <v>-0.7489</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.2688</v>
+        <v>-0.3025</v>
       </c>
       <c r="F60" t="n">
         <v>0.1399</v>
@@ -3206,32 +3206,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>oSee</t>
+          <t>br0</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.299</v>
+        <v>-0.329</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.1579</v>
+        <v>-0.1737</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7603</v>
+        <v>-0.7608</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.299</v>
+        <v>-0.329</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.299</v>
+        <v>-0.4709</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.299</v>
+        <v>-0.4709</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.299</v>
+        <v>-0.4709</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.299</v>
+        <v>-0.4709</v>
       </c>
       <c r="N61" t="n">
         <v>71</v>
@@ -3252,139 +3252,139 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CYPHER</t>
+          <t>Westmelon</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.3214</v>
+        <v>-0.3607</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.1697</v>
+        <v>-0.1905</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7705</v>
+        <v>-0.7749</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.3214</v>
+        <v>-0.3607</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.3214</v>
+        <v>-0.2194</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.3214</v>
+        <v>-0.2194</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.3214</v>
+        <v>-0.2194</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.3214</v>
+        <v>-0.2194</v>
       </c>
       <c r="N62" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ultimate</t>
+          <t>pr1metapz</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.4705</v>
+        <v>-0.3988</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.2485</v>
+        <v>-0.2106</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.8384</v>
+        <v>-0.792</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.4705</v>
+        <v>-0.3988</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.4705</v>
+        <v>-0.2206</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.4705</v>
+        <v>-0.2206</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.4705</v>
+        <v>-0.2206</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.4705</v>
+        <v>-0.2206</v>
       </c>
       <c r="N63" t="n">
-        <v>124</v>
+        <v>84</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>br0</t>
+          <t>ultimate</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.471</v>
+        <v>-0.5341</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.2487</v>
+        <v>-0.2821</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8386</v>
+        <v>-0.8524</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.471</v>
+        <v>-0.5341</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.471</v>
+        <v>-0.4585</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.471</v>
+        <v>-0.4585</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.471</v>
+        <v>-0.4585</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.471</v>
+        <v>-0.4585</v>
       </c>
       <c r="N64" t="n">
-        <v>71</v>
+        <v>124</v>
       </c>
     </row>
     <row r="65">
@@ -3394,31 +3394,31 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.5229</v>
+        <v>-0.6392</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.2761</v>
+        <v>-0.3376</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8622</v>
+        <v>-0.8993</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.5229</v>
+        <v>-0.6392</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.057</v>
+        <v>-0.0568</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.4659</v>
+        <v>-0.4739</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.057</v>
+        <v>-0.0568</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.06</v>
+        <v>-0.0598</v>
       </c>
       <c r="J65" t="n">
-        <v>-0.4659</v>
+        <v>-0.4739</v>
       </c>
       <c r="K65" t="n">
         <v>240</v>
@@ -3427,7 +3427,7 @@
         <v>64</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.5259</v>
+        <v>-0.5337</v>
       </c>
       <c r="N65" t="n">
         <v>304</v>
@@ -3436,93 +3436,93 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>n1ssim</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.5929</v>
+        <v>-0.7425</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.3131</v>
+        <v>-0.3921</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8941</v>
+        <v>-0.9455</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.5929</v>
+        <v>-0.7425</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.5929</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.5929</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5929</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.5929</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="N66" t="n">
-        <v>120</v>
+        <v>84</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>n1ssim</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.5981</v>
+        <v>-0.791</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.3159</v>
+        <v>-0.4177</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8965</v>
+        <v>-0.9671</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.5981</v>
+        <v>-0.791</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.5981</v>
+        <v>-0.5934</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.5981</v>
+        <v>-0.5934</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.5981</v>
+        <v>-0.5934</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.5981</v>
+        <v>-0.5934</v>
       </c>
       <c r="N67" t="n">
-        <v>84</v>
+        <v>120</v>
       </c>
     </row>
     <row r="68">
@@ -3532,28 +3532,28 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.6056</v>
+        <v>-0.8105</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.3198</v>
+        <v>-0.428</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8999</v>
+        <v>-0.9759</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.6056</v>
+        <v>-0.8105</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.6056</v>
+        <v>-0.6057</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.6056</v>
+        <v>-0.6057</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.6056</v>
+        <v>-0.6057</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.6056</v>
+        <v>-0.6057</v>
       </c>
       <c r="N68" t="n">
         <v>124</v>
@@ -3578,28 +3578,28 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.6146</v>
+        <v>-0.8552999999999999</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.3246</v>
+        <v>-0.4517</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.904</v>
+        <v>-0.9959</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.6146</v>
+        <v>-0.8552999999999999</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.6146</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.6146</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.6146</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -3611,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.6146</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="N69" t="n">
         <v>71</v>
@@ -3620,369 +3620,369 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>C4LLM3SU3</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.7863</v>
+        <v>-0.9671</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.4152</v>
+        <v>-0.5107</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9821</v>
+        <v>-1.0458</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.7863</v>
+        <v>-0.9671</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.7863</v>
+        <v>-0.773</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.7863</v>
+        <v>-0.773</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.7863</v>
+        <v>-0.773</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>83</v>
+        <v>202</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.7863</v>
+        <v>-0.773</v>
       </c>
       <c r="N70" t="n">
-        <v>83</v>
+        <v>202</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>CacaNito</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.8087</v>
+        <v>-1.1827</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.4271</v>
+        <v>-0.6246</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9923</v>
+        <v>-1.1421</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.8087</v>
+        <v>-1.1827</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.8087</v>
+        <v>-0.9775</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.8087</v>
+        <v>-0.9775</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.8087</v>
+        <v>-0.9775</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>202</v>
+        <v>84</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.8087</v>
+        <v>-0.9775</v>
       </c>
       <c r="N71" t="n">
-        <v>202</v>
+        <v>84</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CacaNito</t>
+          <t>ztr</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.9772999999999999</v>
+        <v>-1.2148</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.5161</v>
+        <v>-0.6415</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0691</v>
+        <v>-1.1564</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.9772999999999999</v>
+        <v>-1.2148</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.9772999999999999</v>
+        <v>-0.387</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>-0.6796</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.9772999999999999</v>
+        <v>-0.387</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.9772999999999999</v>
+        <v>-0.4072</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>-0.6796</v>
       </c>
       <c r="K72" t="n">
-        <v>84</v>
+        <v>240</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.9772999999999999</v>
+        <v>-1.0868</v>
       </c>
       <c r="N72" t="n">
-        <v>84</v>
+        <v>304</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>EmiliaQAQ</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.0311</v>
+        <v>-1.2187</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.5445</v>
+        <v>-0.6435999999999999</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0936</v>
+        <v>-1.1582</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.0311</v>
+        <v>-1.2187</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.0311</v>
+        <v>-1.1502</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.0311</v>
+        <v>-1.1502</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.0311</v>
+        <v>-1.1502</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.0311</v>
+        <v>-1.1502</v>
       </c>
       <c r="N73" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>skullz</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.0415</v>
+        <v>-1.219</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.55</v>
+        <v>-0.6437</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0983</v>
+        <v>-1.1583</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.0415</v>
+        <v>-1.219</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.0415</v>
+        <v>-1.1177</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.0415</v>
+        <v>-1.1177</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.0415</v>
+        <v>-1.1177</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>158</v>
+        <v>202</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.0415</v>
+        <v>-1.1177</v>
       </c>
       <c r="N74" t="n">
-        <v>158</v>
+        <v>202</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ztr</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.0678</v>
+        <v>-1.2246</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.5639</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1103</v>
+        <v>-1.1608</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.0678</v>
+        <v>-1.2246</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.3869</v>
+        <v>-1.031</v>
       </c>
       <c r="G75" t="n">
-        <v>-0.6808999999999999</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.3869</v>
+        <v>-1.031</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4071</v>
+        <v>-1.031</v>
       </c>
       <c r="J75" t="n">
-        <v>-0.6808999999999999</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>240</v>
+        <v>71</v>
       </c>
       <c r="L75" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.088</v>
+        <v>-1.031</v>
       </c>
       <c r="N75" t="n">
-        <v>304</v>
+        <v>71</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>C4LLM3SU3</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.1297</v>
+        <v>-1.2673</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.5966</v>
+        <v>-0.6693</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1385</v>
+        <v>-1.1799</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.1297</v>
+        <v>-1.2673</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.1297</v>
+        <v>-0.7863</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.1297</v>
+        <v>-0.7863</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.1297</v>
+        <v>-0.7863</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>202</v>
+        <v>83</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.1297</v>
+        <v>-0.7863</v>
       </c>
       <c r="N76" t="n">
-        <v>202</v>
+        <v>83</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EmiliaQAQ</t>
+          <t>skullz</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.1502</v>
+        <v>-1.406</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.6074000000000001</v>
+        <v>-0.7425</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1478</v>
+        <v>-1.2418</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.1502</v>
+        <v>-1.406</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.1502</v>
+        <v>-1.0334</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.1502</v>
+        <v>-1.0334</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.1502</v>
+        <v>-1.0334</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.1502</v>
+        <v>-1.0334</v>
       </c>
       <c r="N77" t="n">
-        <v>83</v>
+        <v>158</v>
       </c>
     </row>
     <row r="78">
@@ -3992,28 +3992,28 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.5355</v>
+        <v>-2.0075</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.8109</v>
+        <v>-1.0602</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.3232</v>
+        <v>-1.5105</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.5355</v>
+        <v>-2.0075</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.5355</v>
+        <v>-1.5353</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.5355</v>
+        <v>-1.5353</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.5355</v>
+        <v>-1.5353</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.5355</v>
+        <v>-1.5353</v>
       </c>
       <c r="N78" t="n">
         <v>71</v>
@@ -4034,93 +4034,93 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>LNZ</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.0607</v>
+        <v>-2.3033</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.0882</v>
+        <v>-1.2164</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.5623</v>
+        <v>-1.6427</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.0607</v>
+        <v>-2.3033</v>
       </c>
       <c r="F79" t="n">
-        <v>-2.0607</v>
+        <v>-2.1768</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-2.0607</v>
+        <v>-2.1768</v>
       </c>
       <c r="I79" t="n">
-        <v>-2.1683</v>
+        <v>-2.1768</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>262</v>
+        <v>144</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-2.1683</v>
+        <v>-2.1768</v>
       </c>
       <c r="N79" t="n">
-        <v>262</v>
+        <v>144</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>LNZ</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.1672</v>
+        <v>-2.4708</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.1445</v>
+        <v>-1.3048</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.6108</v>
+        <v>-1.7175</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.1672</v>
+        <v>-2.4708</v>
       </c>
       <c r="F80" t="n">
-        <v>-2.1672</v>
+        <v>-2.0602</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.1672</v>
+        <v>-2.0602</v>
       </c>
       <c r="I80" t="n">
-        <v>-2.1672</v>
+        <v>-2.1677</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>144</v>
+        <v>262</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>-2.1672</v>
+        <v>-2.1677</v>
       </c>
       <c r="N80" t="n">
-        <v>144</v>
+        <v>262</v>
       </c>
     </row>
     <row r="81">
@@ -4130,16 +4130,16 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3.0971</v>
+        <v>-3.5432</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.6356</v>
+        <v>-1.8711</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.0341</v>
+        <v>-2.1965</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.0971</v>
+        <v>-3.5432</v>
       </c>
       <c r="F81" t="n">
         <v>-2.3811</v>
@@ -4266,13 +4266,13 @@
         <v>24</v>
       </c>
       <c r="H2" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3629</v>
+        <v>0.3811</v>
       </c>
       <c r="J2" t="n">
-        <v>8.7096</v>
+        <v>9.1464</v>
       </c>
     </row>
     <row r="3">
@@ -4309,10 +4309,10 @@
         <v>0.97</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0472</v>
+        <v>-0.0475</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.1328</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="4">
@@ -4349,10 +4349,10 @@
         <v>0.8</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2399</v>
+        <v>-0.2401</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.7576</v>
+        <v>-5.7624</v>
       </c>
     </row>
     <row r="5">
@@ -4389,10 +4389,10 @@
         <v>0.74</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2976</v>
+        <v>-0.2978</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.1424</v>
+        <v>-7.1472</v>
       </c>
     </row>
     <row r="6">
@@ -4429,10 +4429,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3441</v>
+        <v>-0.3443</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.2584</v>
+        <v>-8.263199999999999</v>
       </c>
     </row>
     <row r="7">
@@ -5066,13 +5066,13 @@
         <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5984</v>
+        <v>0.6141</v>
       </c>
       <c r="J22" t="n">
-        <v>12.5664</v>
+        <v>12.8961</v>
       </c>
     </row>
     <row r="23">
@@ -5109,10 +5109,10 @@
         <v>1.14</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3534</v>
+        <v>0.3528</v>
       </c>
       <c r="J23" t="n">
-        <v>7.4214</v>
+        <v>7.4088</v>
       </c>
     </row>
     <row r="24">
@@ -5149,10 +5149,10 @@
         <v>0.8</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2428</v>
+        <v>-0.243</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.0988</v>
+        <v>-5.103</v>
       </c>
     </row>
     <row r="25">
@@ -5189,10 +5189,10 @@
         <v>0.72</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3194</v>
+        <v>-0.3196</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.7074</v>
+        <v>-6.7116</v>
       </c>
     </row>
     <row r="26">
@@ -5229,10 +5229,10 @@
         <v>0.55</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4719</v>
+        <v>-0.4721</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.9099</v>
+        <v>-9.914099999999999</v>
       </c>
     </row>
     <row r="27">
@@ -6266,13 +6266,13 @@
         <v>24</v>
       </c>
       <c r="H52" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6977</v>
+        <v>0.6829</v>
       </c>
       <c r="J52" t="n">
-        <v>16.7448</v>
+        <v>16.3896</v>
       </c>
     </row>
     <row r="53">
@@ -6309,10 +6309,10 @@
         <v>1.22</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5571</v>
+        <v>0.5574</v>
       </c>
       <c r="J53" t="n">
-        <v>13.3704</v>
+        <v>13.3776</v>
       </c>
     </row>
     <row r="54">
@@ -6349,10 +6349,10 @@
         <v>1.1</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3209</v>
+        <v>0.3212</v>
       </c>
       <c r="J54" t="n">
-        <v>7.7016</v>
+        <v>7.7088</v>
       </c>
     </row>
     <row r="55">
@@ -6389,10 +6389,10 @@
         <v>1.03</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1164</v>
+        <v>0.1167</v>
       </c>
       <c r="J55" t="n">
-        <v>2.7936</v>
+        <v>2.8008</v>
       </c>
     </row>
     <row r="56">
@@ -6429,10 +6429,10 @@
         <v>0.99</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.0808</v>
+        <v>-0.0805</v>
       </c>
       <c r="J56" t="n">
-        <v>-1.9392</v>
+        <v>-1.932</v>
       </c>
     </row>
     <row r="57">
@@ -6469,10 +6469,10 @@
         <v>1.33</v>
       </c>
       <c r="I57" t="n">
-        <v>0.577</v>
+        <v>0.5759</v>
       </c>
       <c r="J57" t="n">
-        <v>13.848</v>
+        <v>13.8216</v>
       </c>
     </row>
     <row r="58">
@@ -6506,13 +6506,13 @@
         <v>24</v>
       </c>
       <c r="H58" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3511</v>
+        <v>0.3674</v>
       </c>
       <c r="J58" t="n">
-        <v>8.426399999999999</v>
+        <v>8.817600000000001</v>
       </c>
     </row>
     <row r="59">
@@ -6549,10 +6549,10 @@
         <v>1.09</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2228</v>
+        <v>0.2223</v>
       </c>
       <c r="J59" t="n">
-        <v>5.3472</v>
+        <v>5.3352</v>
       </c>
     </row>
     <row r="60">
@@ -6589,10 +6589,10 @@
         <v>1.07</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1833</v>
+        <v>0.1829</v>
       </c>
       <c r="J60" t="n">
-        <v>4.3992</v>
+        <v>4.3896</v>
       </c>
     </row>
     <row r="61">
@@ -6626,13 +6626,13 @@
         <v>24</v>
       </c>
       <c r="H61" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3536</v>
+        <v>-0.3356</v>
       </c>
       <c r="J61" t="n">
-        <v>-8.4864</v>
+        <v>-8.054399999999999</v>
       </c>
     </row>
     <row r="62">
@@ -7069,10 +7069,10 @@
         <v>1.45</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9096</v>
+        <v>0.9086</v>
       </c>
       <c r="J72" t="n">
-        <v>21.8304</v>
+        <v>21.8064</v>
       </c>
     </row>
     <row r="73">
@@ -7106,13 +7106,13 @@
         <v>24</v>
       </c>
       <c r="H73" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="I73" t="n">
-        <v>0.495</v>
+        <v>0.5112</v>
       </c>
       <c r="J73" t="n">
-        <v>11.88</v>
+        <v>12.2688</v>
       </c>
     </row>
     <row r="74">
@@ -7146,13 +7146,13 @@
         <v>24</v>
       </c>
       <c r="H74" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2156</v>
+        <v>0.2436</v>
       </c>
       <c r="J74" t="n">
-        <v>5.1744</v>
+        <v>5.8464</v>
       </c>
     </row>
     <row r="75">
@@ -7189,10 +7189,10 @@
         <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.0164</v>
+        <v>-0.0171</v>
       </c>
       <c r="J75" t="n">
-        <v>-0.3936</v>
+        <v>-0.4104</v>
       </c>
     </row>
     <row r="76">
@@ -7229,10 +7229,10 @@
         <v>0.83</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.538</v>
+        <v>-0.5387999999999999</v>
       </c>
       <c r="J76" t="n">
-        <v>-12.912</v>
+        <v>-12.9312</v>
       </c>
     </row>
     <row r="77">
@@ -7269,10 +7269,10 @@
         <v>1.12</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2894</v>
+        <v>0.2898</v>
       </c>
       <c r="J77" t="n">
-        <v>6.9456</v>
+        <v>6.9552</v>
       </c>
     </row>
     <row r="78">
@@ -7309,10 +7309,10 @@
         <v>1.1</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2511</v>
+        <v>0.2514</v>
       </c>
       <c r="J78" t="n">
-        <v>6.0264</v>
+        <v>6.0336</v>
       </c>
     </row>
     <row r="79">
@@ -7349,10 +7349,10 @@
         <v>1.04</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1236</v>
+        <v>0.1238</v>
       </c>
       <c r="J79" t="n">
-        <v>2.9664</v>
+        <v>2.9712</v>
       </c>
     </row>
     <row r="80">
@@ -7386,13 +7386,13 @@
         <v>24</v>
       </c>
       <c r="H80" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1476</v>
+        <v>-0.1587</v>
       </c>
       <c r="J80" t="n">
-        <v>-3.5424</v>
+        <v>-3.8088</v>
       </c>
     </row>
     <row r="81">
@@ -7429,10 +7429,10 @@
         <v>0.88</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.17</v>
+        <v>-0.1698</v>
       </c>
       <c r="J81" t="n">
-        <v>-4.08</v>
+        <v>-4.0752</v>
       </c>
     </row>
     <row r="82">
@@ -7869,10 +7869,10 @@
         <v>1.37</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5206</v>
+        <v>0.5199</v>
       </c>
       <c r="J92" t="n">
-        <v>11.4532</v>
+        <v>11.4378</v>
       </c>
     </row>
     <row r="93">
@@ -7906,13 +7906,13 @@
         <v>22</v>
       </c>
       <c r="H93" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3766</v>
+        <v>0.3887</v>
       </c>
       <c r="J93" t="n">
-        <v>8.2852</v>
+        <v>8.551399999999999</v>
       </c>
     </row>
     <row r="94">
@@ -7949,10 +7949,10 @@
         <v>1.02</v>
       </c>
       <c r="I94" t="n">
-        <v>0.0564</v>
+        <v>0.0562</v>
       </c>
       <c r="J94" t="n">
-        <v>1.2408</v>
+        <v>1.2364</v>
       </c>
     </row>
     <row r="95">
@@ -7986,13 +7986,13 @@
         <v>22</v>
       </c>
       <c r="H95" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1922</v>
+        <v>-0.1818</v>
       </c>
       <c r="J95" t="n">
-        <v>-4.2284</v>
+        <v>-3.9996</v>
       </c>
     </row>
     <row r="96">
@@ -8029,10 +8029,10 @@
         <v>0.59</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4471</v>
+        <v>-0.4474</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.8362</v>
+        <v>-9.8428</v>
       </c>
     </row>
     <row r="97">
@@ -8069,10 +8069,10 @@
         <v>1.83</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8231000000000001</v>
+        <v>0.8235</v>
       </c>
       <c r="J97" t="n">
-        <v>18.1082</v>
+        <v>18.117</v>
       </c>
     </row>
     <row r="98">
@@ -8106,13 +8106,13 @@
         <v>22</v>
       </c>
       <c r="H98" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2779</v>
+        <v>0.2658</v>
       </c>
       <c r="J98" t="n">
-        <v>6.1138</v>
+        <v>5.8476</v>
       </c>
     </row>
     <row r="99">
@@ -8149,10 +8149,10 @@
         <v>1.11</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1882</v>
+        <v>0.1884</v>
       </c>
       <c r="J99" t="n">
-        <v>4.1404</v>
+        <v>4.1448</v>
       </c>
     </row>
     <row r="100">
@@ -8189,10 +8189,10 @@
         <v>0.99</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.0366</v>
+        <v>-0.0365</v>
       </c>
       <c r="J100" t="n">
-        <v>-0.8052</v>
+        <v>-0.803</v>
       </c>
     </row>
     <row r="101">
@@ -8229,10 +8229,10 @@
         <v>0.66</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3959</v>
+        <v>-0.3957</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.7098</v>
+        <v>-8.705399999999999</v>
       </c>
     </row>
     <row r="102">
@@ -8266,13 +8266,13 @@
         <v>21</v>
       </c>
       <c r="H102" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I102" t="n">
-        <v>0.9323</v>
+        <v>0.944</v>
       </c>
       <c r="J102" t="n">
-        <v>19.5783</v>
+        <v>19.824</v>
       </c>
     </row>
     <row r="103">
@@ -8309,10 +8309,10 @@
         <v>1.32</v>
       </c>
       <c r="I103" t="n">
-        <v>0.703</v>
+        <v>0.7014</v>
       </c>
       <c r="J103" t="n">
-        <v>14.763</v>
+        <v>14.7294</v>
       </c>
     </row>
     <row r="104">
@@ -8346,13 +8346,13 @@
         <v>21</v>
       </c>
       <c r="H104" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="I104" t="n">
-        <v>0.5342</v>
+        <v>0.5647</v>
       </c>
       <c r="J104" t="n">
-        <v>11.2182</v>
+        <v>11.8587</v>
       </c>
     </row>
     <row r="105">
@@ -8386,13 +8386,13 @@
         <v>21</v>
       </c>
       <c r="H105" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="I105" t="n">
-        <v>0.2861</v>
+        <v>0.3366</v>
       </c>
       <c r="J105" t="n">
-        <v>6.0081</v>
+        <v>7.0686</v>
       </c>
     </row>
     <row r="106">
@@ -8429,10 +8429,10 @@
         <v>0.83</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5528999999999999</v>
+        <v>-0.5547</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.6109</v>
+        <v>-11.6487</v>
       </c>
     </row>
     <row r="107">
@@ -8469,10 +8469,10 @@
         <v>1.11</v>
       </c>
       <c r="I107" t="n">
-        <v>0.2984</v>
+        <v>0.302</v>
       </c>
       <c r="J107" t="n">
-        <v>6.2664</v>
+        <v>6.342</v>
       </c>
     </row>
     <row r="108">
@@ -8509,10 +8509,10 @@
         <v>1.02</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0931</v>
+        <v>0.096</v>
       </c>
       <c r="J108" t="n">
-        <v>1.9551</v>
+        <v>2.016</v>
       </c>
     </row>
     <row r="109">
@@ -8546,13 +8546,13 @@
         <v>21</v>
       </c>
       <c r="H109" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1037</v>
+        <v>-0.1596</v>
       </c>
       <c r="J109" t="n">
-        <v>-2.1777</v>
+        <v>-3.3516</v>
       </c>
     </row>
     <row r="110">
@@ -8586,13 +8586,13 @@
         <v>21</v>
       </c>
       <c r="H110" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2996</v>
+        <v>-0.3078</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.2916</v>
+        <v>-6.4638</v>
       </c>
     </row>
     <row r="111">
@@ -8629,10 +8629,10 @@
         <v>0.64</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3916</v>
+        <v>-0.3904</v>
       </c>
       <c r="J111" t="n">
-        <v>-8.223599999999999</v>
+        <v>-8.198399999999999</v>
       </c>
     </row>
     <row r="112">
@@ -9466,13 +9466,13 @@
         <v>24</v>
       </c>
       <c r="H132" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="I132" t="n">
-        <v>0.7857</v>
+        <v>0.7653</v>
       </c>
       <c r="J132" t="n">
-        <v>18.8568</v>
+        <v>18.3672</v>
       </c>
     </row>
     <row r="133">
@@ -9509,10 +9509,10 @@
         <v>1.24</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6572</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="J133" t="n">
-        <v>15.7728</v>
+        <v>15.7872</v>
       </c>
     </row>
     <row r="134">
@@ -9549,10 +9549,10 @@
         <v>1.1</v>
       </c>
       <c r="I134" t="n">
-        <v>0.3282</v>
+        <v>0.3285</v>
       </c>
       <c r="J134" t="n">
-        <v>7.8768</v>
+        <v>7.884</v>
       </c>
     </row>
     <row r="135">
@@ -9589,10 +9589,10 @@
         <v>0.86</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.4581</v>
+        <v>-0.4577</v>
       </c>
       <c r="J135" t="n">
-        <v>-10.9944</v>
+        <v>-10.9848</v>
       </c>
     </row>
     <row r="136">
@@ -9629,10 +9629,10 @@
         <v>0.84</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.507</v>
+        <v>-0.5067</v>
       </c>
       <c r="J136" t="n">
-        <v>-12.168</v>
+        <v>-12.1608</v>
       </c>
     </row>
     <row r="137">
@@ -11069,10 +11069,10 @@
         <v>1.65</v>
       </c>
       <c r="I172" t="n">
-        <v>0.8807</v>
+        <v>0.88</v>
       </c>
       <c r="J172" t="n">
-        <v>17.614</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="173">
@@ -11106,13 +11106,13 @@
         <v>20</v>
       </c>
       <c r="H173" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="I173" t="n">
-        <v>0.3455</v>
+        <v>0.3585</v>
       </c>
       <c r="J173" t="n">
-        <v>6.91</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="174">
@@ -11149,10 +11149,10 @@
         <v>0.77</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.279</v>
+        <v>-0.2792</v>
       </c>
       <c r="J174" t="n">
-        <v>-5.58</v>
+        <v>-5.584</v>
       </c>
     </row>
     <row r="175">
@@ -11189,10 +11189,10 @@
         <v>0.73</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3171</v>
+        <v>-0.3173</v>
       </c>
       <c r="J175" t="n">
-        <v>-6.342</v>
+        <v>-6.346</v>
       </c>
     </row>
     <row r="176">
@@ -11229,10 +11229,10 @@
         <v>0.5</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5207000000000001</v>
+        <v>-0.5209</v>
       </c>
       <c r="J176" t="n">
-        <v>-10.414</v>
+        <v>-10.418</v>
       </c>
     </row>
     <row r="177">
@@ -14269,10 +14269,10 @@
         <v>1.28</v>
       </c>
       <c r="I252" t="n">
-        <v>0.3996</v>
+        <v>0.3993</v>
       </c>
       <c r="J252" t="n">
-        <v>9.190799999999999</v>
+        <v>9.1839</v>
       </c>
     </row>
     <row r="253">
@@ -14306,13 +14306,13 @@
         <v>23</v>
       </c>
       <c r="H253" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="I253" t="n">
-        <v>0.3051</v>
+        <v>0.317</v>
       </c>
       <c r="J253" t="n">
-        <v>7.0173</v>
+        <v>7.291</v>
       </c>
     </row>
     <row r="254">
@@ -14349,10 +14349,10 @@
         <v>1.17</v>
       </c>
       <c r="I254" t="n">
-        <v>0.268</v>
+        <v>0.2678</v>
       </c>
       <c r="J254" t="n">
-        <v>6.164</v>
+        <v>6.1594</v>
       </c>
     </row>
     <row r="255">
@@ -14389,10 +14389,10 @@
         <v>1.1</v>
       </c>
       <c r="I255" t="n">
-        <v>0.1765</v>
+        <v>0.1764</v>
       </c>
       <c r="J255" t="n">
-        <v>4.0595</v>
+        <v>4.0572</v>
       </c>
     </row>
     <row r="256">
@@ -14429,10 +14429,10 @@
         <v>0.87</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.1908</v>
+        <v>-0.1909</v>
       </c>
       <c r="J256" t="n">
-        <v>-4.3884</v>
+        <v>-4.3907</v>
       </c>
     </row>
     <row r="257">
@@ -15666,13 +15666,13 @@
         <v>19</v>
       </c>
       <c r="H287" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="I287" t="n">
-        <v>0.6726</v>
+        <v>0.663</v>
       </c>
       <c r="J287" t="n">
-        <v>12.7794</v>
+        <v>12.597</v>
       </c>
     </row>
     <row r="288">
@@ -15709,10 +15709,10 @@
         <v>1.43</v>
       </c>
       <c r="I288" t="n">
-        <v>0.5423</v>
+        <v>0.5426</v>
       </c>
       <c r="J288" t="n">
-        <v>10.3037</v>
+        <v>10.3094</v>
       </c>
     </row>
     <row r="289">
@@ -15749,10 +15749,10 @@
         <v>1.27</v>
       </c>
       <c r="I289" t="n">
-        <v>0.374</v>
+        <v>0.3741</v>
       </c>
       <c r="J289" t="n">
-        <v>7.106</v>
+        <v>7.1079</v>
       </c>
     </row>
     <row r="290">
@@ -15789,10 +15789,10 @@
         <v>1.26</v>
       </c>
       <c r="I290" t="n">
-        <v>0.363</v>
+        <v>0.3631</v>
       </c>
       <c r="J290" t="n">
-        <v>6.897</v>
+        <v>6.8989</v>
       </c>
     </row>
     <row r="291">
@@ -15829,10 +15829,10 @@
         <v>0.9</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.1694</v>
+        <v>-0.1693</v>
       </c>
       <c r="J291" t="n">
-        <v>-3.2186</v>
+        <v>-3.2167</v>
       </c>
     </row>
     <row r="292">
@@ -17269,10 +17269,10 @@
         <v>1.48</v>
       </c>
       <c r="I327" t="n">
-        <v>1.0913</v>
+        <v>1.0918</v>
       </c>
       <c r="J327" t="n">
-        <v>32.739</v>
+        <v>32.754</v>
       </c>
     </row>
     <row r="328">
@@ -17309,10 +17309,10 @@
         <v>1.37</v>
       </c>
       <c r="I328" t="n">
-        <v>0.9083</v>
+        <v>0.9089</v>
       </c>
       <c r="J328" t="n">
-        <v>27.249</v>
+        <v>27.267</v>
       </c>
     </row>
     <row r="329">
@@ -17346,13 +17346,13 @@
         <v>30</v>
       </c>
       <c r="H329" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="I329" t="n">
-        <v>0.7669</v>
+        <v>0.7467</v>
       </c>
       <c r="J329" t="n">
-        <v>23.007</v>
+        <v>22.401</v>
       </c>
     </row>
     <row r="330">
@@ -17389,10 +17389,10 @@
         <v>0.96</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.1938</v>
+        <v>-0.1934</v>
       </c>
       <c r="J330" t="n">
-        <v>-5.814</v>
+        <v>-5.802</v>
       </c>
     </row>
     <row r="331">
@@ -17429,10 +17429,10 @@
         <v>0.57</v>
       </c>
       <c r="I331" t="n">
-        <v>-1.1005</v>
+        <v>-1.1002</v>
       </c>
       <c r="J331" t="n">
-        <v>-33.015</v>
+        <v>-33.006</v>
       </c>
     </row>
     <row r="332">
@@ -19158,7 +19158,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -19438,7 +19438,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -19869,10 +19869,10 @@
         <v>1.57</v>
       </c>
       <c r="I392" t="n">
-        <v>1.2177</v>
+        <v>1.2171</v>
       </c>
       <c r="J392" t="n">
-        <v>26.7894</v>
+        <v>26.7762</v>
       </c>
     </row>
     <row r="393">
@@ -19909,10 +19909,10 @@
         <v>1.28</v>
       </c>
       <c r="I393" t="n">
-        <v>0.7269</v>
+        <v>0.7264</v>
       </c>
       <c r="J393" t="n">
-        <v>15.9918</v>
+        <v>15.9808</v>
       </c>
     </row>
     <row r="394">
@@ -19949,10 +19949,10 @@
         <v>0.98</v>
       </c>
       <c r="I394" t="n">
-        <v>-0.1223</v>
+        <v>-0.1226</v>
       </c>
       <c r="J394" t="n">
-        <v>-2.6906</v>
+        <v>-2.6972</v>
       </c>
     </row>
     <row r="395">
@@ -19989,10 +19989,10 @@
         <v>0.92</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.3128</v>
+        <v>-0.3132</v>
       </c>
       <c r="J395" t="n">
-        <v>-6.8816</v>
+        <v>-6.8904</v>
       </c>
     </row>
     <row r="396">
@@ -20026,13 +20026,13 @@
         <v>22</v>
       </c>
       <c r="H396" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.3674</v>
+        <v>-0.3408</v>
       </c>
       <c r="J396" t="n">
-        <v>-8.082800000000001</v>
+        <v>-7.4976</v>
       </c>
     </row>
     <row r="397">
@@ -23469,10 +23469,10 @@
         <v>1.32</v>
       </c>
       <c r="I482" t="n">
-        <v>0.8243</v>
+        <v>0.8249</v>
       </c>
       <c r="J482" t="n">
-        <v>29.6748</v>
+        <v>29.6964</v>
       </c>
     </row>
     <row r="483">
@@ -23509,10 +23509,10 @@
         <v>1.23</v>
       </c>
       <c r="I483" t="n">
-        <v>0.6327</v>
+        <v>0.6332</v>
       </c>
       <c r="J483" t="n">
-        <v>22.7772</v>
+        <v>22.7952</v>
       </c>
     </row>
     <row r="484">
@@ -23549,10 +23549,10 @@
         <v>1.23</v>
       </c>
       <c r="I484" t="n">
-        <v>0.6327</v>
+        <v>0.6332</v>
       </c>
       <c r="J484" t="n">
-        <v>22.7772</v>
+        <v>22.7952</v>
       </c>
     </row>
     <row r="485">
@@ -23586,13 +23586,13 @@
         <v>36</v>
       </c>
       <c r="H485" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="I485" t="n">
-        <v>0.2745</v>
+        <v>0.2477</v>
       </c>
       <c r="J485" t="n">
-        <v>9.882</v>
+        <v>8.917199999999999</v>
       </c>
     </row>
     <row r="486">
@@ -23629,10 +23629,10 @@
         <v>0.53</v>
       </c>
       <c r="I486" t="n">
-        <v>-1.1706</v>
+        <v>-1.1703</v>
       </c>
       <c r="J486" t="n">
-        <v>-42.1416</v>
+        <v>-42.1308</v>
       </c>
     </row>
     <row r="487">
@@ -23669,10 +23669,10 @@
         <v>1.3</v>
       </c>
       <c r="I487" t="n">
-        <v>0.5903</v>
+        <v>0.5898</v>
       </c>
       <c r="J487" t="n">
-        <v>21.2508</v>
+        <v>21.2328</v>
       </c>
     </row>
     <row r="488">
@@ -23709,10 +23709,10 @@
         <v>1.2</v>
       </c>
       <c r="I488" t="n">
-        <v>0.4279</v>
+        <v>0.4275</v>
       </c>
       <c r="J488" t="n">
-        <v>15.4044</v>
+        <v>15.39</v>
       </c>
     </row>
     <row r="489">
@@ -23746,13 +23746,13 @@
         <v>36</v>
       </c>
       <c r="H489" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="I489" t="n">
-        <v>-0.1376</v>
+        <v>-0.126</v>
       </c>
       <c r="J489" t="n">
-        <v>-4.9536</v>
+        <v>-4.536</v>
       </c>
     </row>
     <row r="490">
@@ -23789,10 +23789,10 @@
         <v>0.9</v>
       </c>
       <c r="I490" t="n">
-        <v>-0.1492</v>
+        <v>-0.1493</v>
       </c>
       <c r="J490" t="n">
-        <v>-5.3712</v>
+        <v>-5.3748</v>
       </c>
     </row>
     <row r="491">
@@ -23829,10 +23829,10 @@
         <v>0.82</v>
       </c>
       <c r="I491" t="n">
-        <v>-0.2347</v>
+        <v>-0.2349</v>
       </c>
       <c r="J491" t="n">
-        <v>-8.449199999999999</v>
+        <v>-8.4564</v>
       </c>
     </row>
     <row r="492">
@@ -23866,13 +23866,13 @@
         <v>18</v>
       </c>
       <c r="H492" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="I492" t="n">
-        <v>-0.1102</v>
+        <v>-0.0982</v>
       </c>
       <c r="J492" t="n">
-        <v>-1.9836</v>
+        <v>-1.7676</v>
       </c>
     </row>
     <row r="493">
@@ -23909,10 +23909,10 @@
         <v>0.84</v>
       </c>
       <c r="I493" t="n">
-        <v>-0.1895</v>
+        <v>-0.1898</v>
       </c>
       <c r="J493" t="n">
-        <v>-3.411</v>
+        <v>-3.4164</v>
       </c>
     </row>
     <row r="494">
@@ -23949,10 +23949,10 @@
         <v>0.76</v>
       </c>
       <c r="I494" t="n">
-        <v>-0.2684</v>
+        <v>-0.2685</v>
       </c>
       <c r="J494" t="n">
-        <v>-4.8312</v>
+        <v>-4.833</v>
       </c>
     </row>
     <row r="495">
@@ -23989,10 +23989,10 @@
         <v>0.65</v>
       </c>
       <c r="I495" t="n">
-        <v>-0.368</v>
+        <v>-0.3682</v>
       </c>
       <c r="J495" t="n">
-        <v>-6.624</v>
+        <v>-6.6276</v>
       </c>
     </row>
     <row r="496">
@@ -24029,10 +24029,10 @@
         <v>0.62</v>
       </c>
       <c r="I496" t="n">
-        <v>-0.3949</v>
+        <v>-0.3952</v>
       </c>
       <c r="J496" t="n">
-        <v>-7.1082</v>
+        <v>-7.1136</v>
       </c>
     </row>
     <row r="497">
@@ -24269,10 +24269,10 @@
         <v>1.82</v>
       </c>
       <c r="I502" t="n">
-        <v>1.5199</v>
+        <v>1.5205</v>
       </c>
       <c r="J502" t="n">
-        <v>36.4776</v>
+        <v>36.492</v>
       </c>
     </row>
     <row r="503">
@@ -24306,13 +24306,13 @@
         <v>24</v>
       </c>
       <c r="H503" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="I503" t="n">
-        <v>1.044</v>
+        <v>1.0293</v>
       </c>
       <c r="J503" t="n">
-        <v>25.056</v>
+        <v>24.7032</v>
       </c>
     </row>
     <row r="504">
@@ -24349,10 +24349,10 @@
         <v>1.27</v>
       </c>
       <c r="I504" t="n">
-        <v>0.6889</v>
+        <v>0.6892</v>
       </c>
       <c r="J504" t="n">
-        <v>16.5336</v>
+        <v>16.5408</v>
       </c>
     </row>
     <row r="505">
@@ -24389,10 +24389,10 @@
         <v>1.1</v>
       </c>
       <c r="I505" t="n">
-        <v>0.3073</v>
+        <v>0.3076</v>
       </c>
       <c r="J505" t="n">
-        <v>7.3752</v>
+        <v>7.3824</v>
       </c>
     </row>
     <row r="506">
@@ -24429,10 +24429,10 @@
         <v>0.44</v>
       </c>
       <c r="I506" t="n">
-        <v>-1.361</v>
+        <v>-1.3608</v>
       </c>
       <c r="J506" t="n">
-        <v>-32.664</v>
+        <v>-32.6592</v>
       </c>
     </row>
     <row r="507">
@@ -24469,10 +24469,10 @@
         <v>1.34</v>
       </c>
       <c r="I507" t="n">
-        <v>0.672</v>
+        <v>0.6713</v>
       </c>
       <c r="J507" t="n">
-        <v>16.128</v>
+        <v>16.1112</v>
       </c>
     </row>
     <row r="508">
@@ -24506,13 +24506,13 @@
         <v>24</v>
       </c>
       <c r="H508" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="I508" t="n">
-        <v>0.4433</v>
+        <v>0.4599</v>
       </c>
       <c r="J508" t="n">
-        <v>10.6392</v>
+        <v>11.0376</v>
       </c>
     </row>
     <row r="509">
@@ -24549,10 +24549,10 @@
         <v>1.06</v>
       </c>
       <c r="I509" t="n">
-        <v>0.1766</v>
+        <v>0.1762</v>
       </c>
       <c r="J509" t="n">
-        <v>4.2384</v>
+        <v>4.2288</v>
       </c>
     </row>
     <row r="510">
@@ -24589,10 +24589,10 @@
         <v>0.84</v>
       </c>
       <c r="I510" t="n">
-        <v>-0.2084</v>
+        <v>-0.2086</v>
       </c>
       <c r="J510" t="n">
-        <v>-5.0016</v>
+        <v>-5.0064</v>
       </c>
     </row>
     <row r="511">
@@ -24629,10 +24629,10 @@
         <v>0.37</v>
       </c>
       <c r="I511" t="n">
-        <v>-0.6281</v>
+        <v>-0.6282</v>
       </c>
       <c r="J511" t="n">
-        <v>-15.0744</v>
+        <v>-15.0768</v>
       </c>
     </row>
     <row r="512">
@@ -26069,10 +26069,10 @@
         <v>1.4</v>
       </c>
       <c r="I547" t="n">
-        <v>0.9479</v>
+        <v>0.9484</v>
       </c>
       <c r="J547" t="n">
-        <v>21.8017</v>
+        <v>21.8132</v>
       </c>
     </row>
     <row r="548">
@@ -26109,10 +26109,10 @@
         <v>1.36</v>
       </c>
       <c r="I548" t="n">
-        <v>0.8716</v>
+        <v>0.872</v>
       </c>
       <c r="J548" t="n">
-        <v>20.0468</v>
+        <v>20.056</v>
       </c>
     </row>
     <row r="549">
@@ -26146,13 +26146,13 @@
         <v>23</v>
       </c>
       <c r="H549" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="I549" t="n">
-        <v>0.8322000000000001</v>
+        <v>0.8127</v>
       </c>
       <c r="J549" t="n">
-        <v>19.1406</v>
+        <v>18.6921</v>
       </c>
     </row>
     <row r="550">
@@ -26189,10 +26189,10 @@
         <v>1.16</v>
       </c>
       <c r="I550" t="n">
-        <v>0.4563</v>
+        <v>0.4565</v>
       </c>
       <c r="J550" t="n">
-        <v>10.4949</v>
+        <v>10.4995</v>
       </c>
     </row>
     <row r="551">
@@ -26229,10 +26229,10 @@
         <v>0.76</v>
       </c>
       <c r="I551" t="n">
-        <v>-0.716</v>
+        <v>-0.7157</v>
       </c>
       <c r="J551" t="n">
-        <v>-16.468</v>
+        <v>-16.4611</v>
       </c>
     </row>
     <row r="552">
@@ -27469,10 +27469,10 @@
         <v>1.94</v>
       </c>
       <c r="I582" t="n">
-        <v>1.6297</v>
+        <v>1.6302</v>
       </c>
       <c r="J582" t="n">
-        <v>30.9643</v>
+        <v>30.9738</v>
       </c>
     </row>
     <row r="583">
@@ -27509,10 +27509,10 @@
         <v>1.5</v>
       </c>
       <c r="I583" t="n">
-        <v>1.0769</v>
+        <v>1.0772</v>
       </c>
       <c r="J583" t="n">
-        <v>20.4611</v>
+        <v>20.4668</v>
       </c>
     </row>
     <row r="584">
@@ -27549,10 +27549,10 @@
         <v>1.44</v>
       </c>
       <c r="I584" t="n">
-        <v>0.9892</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="J584" t="n">
-        <v>18.7948</v>
+        <v>18.7986</v>
       </c>
     </row>
     <row r="585">
@@ -27586,13 +27586,13 @@
         <v>19</v>
       </c>
       <c r="H585" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="I585" t="n">
-        <v>0.1438</v>
+        <v>0.1124</v>
       </c>
       <c r="J585" t="n">
-        <v>2.7322</v>
+        <v>2.1356</v>
       </c>
     </row>
     <row r="586">
@@ -27629,10 +27629,10 @@
         <v>0.85</v>
       </c>
       <c r="I586" t="n">
-        <v>-0.5318000000000001</v>
+        <v>-0.5315</v>
       </c>
       <c r="J586" t="n">
-        <v>-10.1042</v>
+        <v>-10.0985</v>
       </c>
     </row>
     <row r="587">
@@ -27758,7 +27758,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -28038,7 +28038,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -28269,10 +28269,10 @@
         <v>1.65</v>
       </c>
       <c r="I602" t="n">
-        <v>1.2902</v>
+        <v>1.2907</v>
       </c>
       <c r="J602" t="n">
-        <v>24.5138</v>
+        <v>24.5233</v>
       </c>
     </row>
     <row r="603">
@@ -28309,10 +28309,10 @@
         <v>1.51</v>
       </c>
       <c r="I603" t="n">
-        <v>1.1051</v>
+        <v>1.1054</v>
       </c>
       <c r="J603" t="n">
-        <v>20.9969</v>
+        <v>21.0026</v>
       </c>
     </row>
     <row r="604">
@@ -28346,13 +28346,13 @@
         <v>19</v>
       </c>
       <c r="H604" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="I604" t="n">
-        <v>0.4001</v>
+        <v>0.3761</v>
       </c>
       <c r="J604" t="n">
-        <v>7.6019</v>
+        <v>7.1459</v>
       </c>
     </row>
     <row r="605">
@@ -28389,10 +28389,10 @@
         <v>1.08</v>
       </c>
       <c r="I605" t="n">
-        <v>0.246</v>
+        <v>0.2463</v>
       </c>
       <c r="J605" t="n">
-        <v>4.674</v>
+        <v>4.6797</v>
       </c>
     </row>
     <row r="606">
@@ -28429,10 +28429,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I606" t="n">
-        <v>-0.2787</v>
+        <v>-0.2784</v>
       </c>
       <c r="J606" t="n">
-        <v>-5.2953</v>
+        <v>-5.2896</v>
       </c>
     </row>
     <row r="607">
@@ -28466,13 +28466,13 @@
         <v>19</v>
       </c>
       <c r="H607" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="I607" t="n">
-        <v>0.3146</v>
+        <v>0.2955</v>
       </c>
       <c r="J607" t="n">
-        <v>5.9774</v>
+        <v>5.6145</v>
       </c>
     </row>
     <row r="608">
@@ -28509,10 +28509,10 @@
         <v>0.88</v>
       </c>
       <c r="I608" t="n">
-        <v>-0.1609</v>
+        <v>-0.1608</v>
       </c>
       <c r="J608" t="n">
-        <v>-3.0571</v>
+        <v>-3.0552</v>
       </c>
     </row>
     <row r="609">
@@ -28549,10 +28549,10 @@
         <v>0.87</v>
       </c>
       <c r="I609" t="n">
-        <v>-0.1715</v>
+        <v>-0.1714</v>
       </c>
       <c r="J609" t="n">
-        <v>-3.2585</v>
+        <v>-3.2566</v>
       </c>
     </row>
     <row r="610">
@@ -28589,10 +28589,10 @@
         <v>0.83</v>
       </c>
       <c r="I610" t="n">
-        <v>-0.213</v>
+        <v>-0.2128</v>
       </c>
       <c r="J610" t="n">
-        <v>-4.047</v>
+        <v>-4.0432</v>
       </c>
     </row>
     <row r="611">
@@ -28629,10 +28629,10 @@
         <v>0.8</v>
       </c>
       <c r="I611" t="n">
-        <v>-0.243</v>
+        <v>-0.2428</v>
       </c>
       <c r="J611" t="n">
-        <v>-4.617</v>
+        <v>-4.6132</v>
       </c>
     </row>
     <row r="612">
@@ -28878,7 +28878,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>Jeorge</t>
+          <t>oSee</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
@@ -28918,7 +28918,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>oSee</t>
+          <t>Jeorge</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -29669,10 +29669,10 @@
         <v>1.12</v>
       </c>
       <c r="I637" t="n">
-        <v>0.303</v>
+        <v>0.3025</v>
       </c>
       <c r="J637" t="n">
-        <v>6.666</v>
+        <v>6.655</v>
       </c>
     </row>
     <row r="638">
@@ -29706,13 +29706,13 @@
         <v>22</v>
       </c>
       <c r="H638" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="I638" t="n">
-        <v>0.2232</v>
+        <v>0.2434</v>
       </c>
       <c r="J638" t="n">
-        <v>4.9104</v>
+        <v>5.3548</v>
       </c>
     </row>
     <row r="639">
@@ -29749,10 +29749,10 @@
         <v>0.97</v>
       </c>
       <c r="I639" t="n">
-        <v>-0.055</v>
+        <v>-0.0552</v>
       </c>
       <c r="J639" t="n">
-        <v>-1.21</v>
+        <v>-1.2144</v>
       </c>
     </row>
     <row r="640">
@@ -29789,10 +29789,10 @@
         <v>0.89</v>
       </c>
       <c r="I640" t="n">
-        <v>-0.1534</v>
+        <v>-0.1536</v>
       </c>
       <c r="J640" t="n">
-        <v>-3.3748</v>
+        <v>-3.3792</v>
       </c>
     </row>
     <row r="641">
@@ -29829,10 +29829,10 @@
         <v>0.66</v>
       </c>
       <c r="I641" t="n">
-        <v>-0.379</v>
+        <v>-0.3792</v>
       </c>
       <c r="J641" t="n">
-        <v>-8.337999999999999</v>
+        <v>-8.3424</v>
       </c>
     </row>
     <row r="642">
@@ -30269,10 +30269,10 @@
         <v>1.48</v>
       </c>
       <c r="I652" t="n">
-        <v>1.0845</v>
+        <v>1.0841</v>
       </c>
       <c r="J652" t="n">
-        <v>26.028</v>
+        <v>26.0184</v>
       </c>
     </row>
     <row r="653">
@@ -30309,10 +30309,10 @@
         <v>1.13</v>
       </c>
       <c r="I653" t="n">
-        <v>0.391</v>
+        <v>0.3907</v>
       </c>
       <c r="J653" t="n">
-        <v>9.384</v>
+        <v>9.376799999999999</v>
       </c>
     </row>
     <row r="654">
@@ -30346,13 +30346,13 @@
         <v>24</v>
       </c>
       <c r="H654" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="I654" t="n">
-        <v>0.3416</v>
+        <v>0.3663</v>
       </c>
       <c r="J654" t="n">
-        <v>8.198399999999999</v>
+        <v>8.7912</v>
       </c>
     </row>
     <row r="655">
@@ -30389,10 +30389,10 @@
         <v>1.11</v>
       </c>
       <c r="I655" t="n">
-        <v>0.3416</v>
+        <v>0.3413</v>
       </c>
       <c r="J655" t="n">
-        <v>8.198399999999999</v>
+        <v>8.1912</v>
       </c>
     </row>
     <row r="656">
@@ -30429,10 +30429,10 @@
         <v>0.99</v>
       </c>
       <c r="I656" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="J656" t="n">
-        <v>-2.088</v>
+        <v>-2.0976</v>
       </c>
     </row>
     <row r="657">
@@ -30669,10 +30669,10 @@
         <v>1.53</v>
       </c>
       <c r="I662" t="n">
-        <v>0.6335</v>
+        <v>0.6332</v>
       </c>
       <c r="J662" t="n">
-        <v>10.7695</v>
+        <v>10.7644</v>
       </c>
     </row>
     <row r="663">
@@ -30709,10 +30709,10 @@
         <v>1.49</v>
       </c>
       <c r="I663" t="n">
-        <v>0.5943000000000001</v>
+        <v>0.5942</v>
       </c>
       <c r="J663" t="n">
-        <v>10.1031</v>
+        <v>10.1014</v>
       </c>
     </row>
     <row r="664">
@@ -30749,10 +30749,10 @@
         <v>1.41</v>
       </c>
       <c r="I664" t="n">
-        <v>0.5148</v>
+        <v>0.5147</v>
       </c>
       <c r="J664" t="n">
-        <v>8.7516</v>
+        <v>8.7499</v>
       </c>
     </row>
     <row r="665">
@@ -30789,10 +30789,10 @@
         <v>1.33</v>
       </c>
       <c r="I665" t="n">
-        <v>0.4337</v>
+        <v>0.4336</v>
       </c>
       <c r="J665" t="n">
-        <v>7.3729</v>
+        <v>7.3712</v>
       </c>
     </row>
     <row r="666">
@@ -30826,13 +30826,13 @@
         <v>17</v>
       </c>
       <c r="H666" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="I666" t="n">
-        <v>0.0948</v>
+        <v>0.1106</v>
       </c>
       <c r="J666" t="n">
-        <v>1.6116</v>
+        <v>1.8802</v>
       </c>
     </row>
     <row r="667">
@@ -30866,13 +30866,13 @@
         <v>17</v>
       </c>
       <c r="H667" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="I667" t="n">
-        <v>0.3515</v>
+        <v>0.3643</v>
       </c>
       <c r="J667" t="n">
-        <v>5.9755</v>
+        <v>6.1931</v>
       </c>
     </row>
     <row r="668">
@@ -30909,10 +30909,10 @@
         <v>1.15</v>
       </c>
       <c r="I668" t="n">
-        <v>0.2944</v>
+        <v>0.2934</v>
       </c>
       <c r="J668" t="n">
-        <v>5.0048</v>
+        <v>4.9878</v>
       </c>
     </row>
     <row r="669">
@@ -30946,13 +30946,13 @@
         <v>17</v>
       </c>
       <c r="H669" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="I669" t="n">
-        <v>-0.1273</v>
+        <v>-0.1159</v>
       </c>
       <c r="J669" t="n">
-        <v>-2.1641</v>
+        <v>-1.9703</v>
       </c>
     </row>
     <row r="670">
@@ -30989,10 +30989,10 @@
         <v>0.72</v>
       </c>
       <c r="I670" t="n">
-        <v>-0.3182</v>
+        <v>-0.3186</v>
       </c>
       <c r="J670" t="n">
-        <v>-5.4094</v>
+        <v>-5.4162</v>
       </c>
     </row>
     <row r="671">
@@ -31029,10 +31029,10 @@
         <v>0.46</v>
       </c>
       <c r="I671" t="n">
-        <v>-0.5478</v>
+        <v>-0.5482</v>
       </c>
       <c r="J671" t="n">
-        <v>-9.3126</v>
+        <v>-9.3194</v>
       </c>
     </row>
     <row r="672">
@@ -31466,13 +31466,13 @@
         <v>24</v>
       </c>
       <c r="H682" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="I682" t="n">
-        <v>0.6642</v>
+        <v>0.6784</v>
       </c>
       <c r="J682" t="n">
-        <v>15.9408</v>
+        <v>16.2816</v>
       </c>
     </row>
     <row r="683">
@@ -31506,13 +31506,13 @@
         <v>24</v>
       </c>
       <c r="H683" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="I683" t="n">
-        <v>0.2148</v>
+        <v>0.2345</v>
       </c>
       <c r="J683" t="n">
-        <v>5.1552</v>
+        <v>5.628</v>
       </c>
     </row>
     <row r="684">
@@ -31549,10 +31549,10 @@
         <v>0.97</v>
       </c>
       <c r="I684" t="n">
-        <v>-0.0573</v>
+        <v>-0.0575</v>
       </c>
       <c r="J684" t="n">
-        <v>-1.3752</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="685">
@@ -31589,10 +31589,10 @@
         <v>0.78</v>
       </c>
       <c r="I685" t="n">
-        <v>-0.2708</v>
+        <v>-0.2712</v>
       </c>
       <c r="J685" t="n">
-        <v>-6.4992</v>
+        <v>-6.5088</v>
       </c>
     </row>
     <row r="686">
@@ -31629,10 +31629,10 @@
         <v>0.76</v>
       </c>
       <c r="I686" t="n">
-        <v>-0.2901</v>
+        <v>-0.2905</v>
       </c>
       <c r="J686" t="n">
-        <v>-6.9624</v>
+        <v>-6.972</v>
       </c>
     </row>
     <row r="687">
@@ -31866,13 +31866,13 @@
         <v>23</v>
       </c>
       <c r="H692" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="I692" t="n">
-        <v>1.6356</v>
+        <v>1.6473</v>
       </c>
       <c r="J692" t="n">
-        <v>37.6188</v>
+        <v>37.8879</v>
       </c>
     </row>
     <row r="693">
@@ -31909,10 +31909,10 @@
         <v>1.28</v>
       </c>
       <c r="I693" t="n">
-        <v>0.7049</v>
+        <v>0.7046</v>
       </c>
       <c r="J693" t="n">
-        <v>16.2127</v>
+        <v>16.2058</v>
       </c>
     </row>
     <row r="694">
@@ -31949,10 +31949,10 @@
         <v>1.21</v>
       </c>
       <c r="I694" t="n">
-        <v>0.5616</v>
+        <v>0.5613</v>
       </c>
       <c r="J694" t="n">
-        <v>12.9168</v>
+        <v>12.9099</v>
       </c>
     </row>
     <row r="695">
@@ -31989,10 +31989,10 @@
         <v>0.93</v>
       </c>
       <c r="I695" t="n">
-        <v>-0.3054</v>
+        <v>-0.3057</v>
       </c>
       <c r="J695" t="n">
-        <v>-7.0242</v>
+        <v>-7.0311</v>
       </c>
     </row>
     <row r="696">
@@ -32029,10 +32029,10 @@
         <v>0.9</v>
       </c>
       <c r="I696" t="n">
-        <v>-0.3883</v>
+        <v>-0.3887</v>
       </c>
       <c r="J696" t="n">
-        <v>-8.930899999999999</v>
+        <v>-8.940099999999999</v>
       </c>
     </row>
     <row r="697">
@@ -32269,10 +32269,10 @@
         <v>1.5</v>
       </c>
       <c r="I702" t="n">
-        <v>1.0912</v>
+        <v>1.0916</v>
       </c>
       <c r="J702" t="n">
-        <v>25.0976</v>
+        <v>25.1068</v>
       </c>
     </row>
     <row r="703">
@@ -32306,13 +32306,13 @@
         <v>23</v>
       </c>
       <c r="H703" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="I703" t="n">
-        <v>1.0636</v>
+        <v>1.0497</v>
       </c>
       <c r="J703" t="n">
-        <v>24.4628</v>
+        <v>24.1431</v>
       </c>
     </row>
     <row r="704">
@@ -32349,10 +32349,10 @@
         <v>1.39</v>
       </c>
       <c r="I704" t="n">
-        <v>0.9164</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="J704" t="n">
-        <v>21.0772</v>
+        <v>21.0864</v>
       </c>
     </row>
     <row r="705">
@@ -32389,10 +32389,10 @@
         <v>1.22</v>
       </c>
       <c r="I705" t="n">
-        <v>0.5807</v>
+        <v>0.5809</v>
       </c>
       <c r="J705" t="n">
-        <v>13.3561</v>
+        <v>13.3607</v>
       </c>
     </row>
     <row r="706">
@@ -32429,10 +32429,10 @@
         <v>0.74</v>
       </c>
       <c r="I706" t="n">
-        <v>-0.7694</v>
+        <v>-0.7691</v>
       </c>
       <c r="J706" t="n">
-        <v>-17.6962</v>
+        <v>-17.6893</v>
       </c>
     </row>
     <row r="707">
@@ -32469,10 +32469,10 @@
         <v>1.32</v>
       </c>
       <c r="I707" t="n">
-        <v>0.653</v>
+        <v>0.6515</v>
       </c>
       <c r="J707" t="n">
-        <v>15.019</v>
+        <v>14.9845</v>
       </c>
     </row>
     <row r="708">
@@ -32506,13 +32506,13 @@
         <v>23</v>
       </c>
       <c r="H708" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="I708" t="n">
-        <v>0.206</v>
+        <v>0.2263</v>
       </c>
       <c r="J708" t="n">
-        <v>4.738</v>
+        <v>5.2049</v>
       </c>
     </row>
     <row r="709">
@@ -32549,10 +32549,10 @@
         <v>0.9</v>
       </c>
       <c r="I709" t="n">
-        <v>-0.1409</v>
+        <v>-0.1412</v>
       </c>
       <c r="J709" t="n">
-        <v>-3.2407</v>
+        <v>-3.2476</v>
       </c>
     </row>
     <row r="710">
@@ -32589,10 +32589,10 @@
         <v>0.85</v>
       </c>
       <c r="I710" t="n">
-        <v>-0.1948</v>
+        <v>-0.1951</v>
       </c>
       <c r="J710" t="n">
-        <v>-4.4804</v>
+        <v>-4.4873</v>
       </c>
     </row>
     <row r="711">
@@ -32626,13 +32626,13 @@
         <v>23</v>
       </c>
       <c r="H711" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="I711" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-0.5175999999999999</v>
       </c>
       <c r="J711" t="n">
-        <v>-12.0911</v>
+        <v>-11.9048</v>
       </c>
     </row>
   </sheetData>
